--- a/카드_아키타입/11_헤어세정.xlsx
+++ b/카드_아키타입/11_헤어세정.xlsx
@@ -199,13 +199,8 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  <absoluteAnchor>
+    <pos x="6162675" y="0"/>
     <ext cx="1143000" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -223,14 +218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="7404100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -248,14 +238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="7404100"/>
     <ext cx="1809750" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -273,14 +258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="7404100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -298,14 +278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="7404100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -323,14 +298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="9251950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -348,14 +318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>10</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="9251950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -373,14 +338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>10</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="9251950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -398,14 +358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>10</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="9251950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -423,14 +378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="11099800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -448,14 +398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>10</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="11099800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -473,14 +418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>10</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="11099800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -498,14 +438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>24</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="22123400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -523,14 +458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>24</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="22123400"/>
     <ext cx="1809750" cy="1657350"/>
     <pic>
       <nvPicPr>
@@ -548,14 +478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>24</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="22123400"/>
     <ext cx="1638300" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -573,14 +498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>37</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="38874700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -598,14 +518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>37</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="38874700"/>
     <ext cx="1809750" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -623,14 +538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>37</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="38874700"/>
     <ext cx="1809750" cy="1028700"/>
     <pic>
       <nvPicPr>
@@ -648,14 +558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>37</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="38874700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -673,14 +578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>37</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="40722550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -698,14 +598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>37</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="40722550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -723,14 +618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>37</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="40722550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -748,14 +638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>37</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="40722550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -773,14 +658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>37</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="42570400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -798,14 +678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>37</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="42570400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -823,14 +698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>37</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="42570400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -848,14 +718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>37</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="42570400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -873,14 +738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>47</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="46913800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -898,14 +758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>47</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="46913800"/>
     <ext cx="1809750" cy="1419225"/>
     <pic>
       <nvPicPr>
@@ -923,14 +778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>47</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="46913800"/>
     <ext cx="1809750" cy="1028700"/>
     <pic>
       <nvPicPr>
@@ -948,14 +798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>47</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="46913800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -973,14 +818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>47</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="48761650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -998,14 +838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>47</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="48761650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1023,14 +858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>47</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="48761650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1048,14 +878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>47</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="48761650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1073,14 +898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>47</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="50609500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1098,14 +918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>47</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="50609500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1123,14 +938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>47</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="50609500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1148,14 +958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>47</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="50609500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1173,14 +978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>59</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="58991500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1198,14 +998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>59</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="58991500"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -1223,14 +1018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>59</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="58991500"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -1248,14 +1038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>59</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="58991500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1273,14 +1058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>59</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="60839350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1298,14 +1078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>59</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="60839350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1323,14 +1098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>59</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="60839350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1348,14 +1118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>59</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="60839350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1373,14 +1138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>59</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="62687200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1398,14 +1158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>59</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="62687200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1423,14 +1178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>59</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="62687200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1448,14 +1198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>59</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="62687200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1473,14 +1218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>59</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="64535050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1498,14 +1238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>59</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="64535050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1523,14 +1258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>59</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="64535050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1548,14 +1278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>69</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="70053200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1573,14 +1298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>69</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="70053200"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1598,14 +1318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>69</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="70053200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1623,14 +1338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>69</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="70053200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1648,14 +1358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>69</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="71901050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1673,14 +1378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>69</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="71901050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1698,14 +1398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>69</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="71901050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1723,14 +1418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>69</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="71901050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1748,14 +1438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>69</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="73748900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1773,14 +1458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>69</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="73748900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1798,14 +1478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>69</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="73748900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1823,14 +1498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>79</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="77254100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1848,14 +1518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>79</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="77254100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1873,14 +1538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>79</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="77254100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1898,14 +1558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>79</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="77254100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1923,14 +1578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>79</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="79101950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1948,14 +1598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>79</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="79101950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1973,14 +1618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>79</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="79101950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1998,14 +1638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>79</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="79101950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2023,14 +1658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>92</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="83235800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2048,14 +1678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>92</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="83235800"/>
     <ext cx="1514475" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2073,14 +1698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>92</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="83235800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2098,14 +1718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>92</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="83235800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2123,14 +1738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>92</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="85083650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2148,14 +1758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>92</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="85083650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2173,14 +1778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>92</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="85083650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2198,14 +1798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>92</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="85083650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2223,14 +1818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>104</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="89420700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2248,14 +1838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>104</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="89420700"/>
     <ext cx="1514475" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2273,14 +1858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>104</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="89420700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2298,14 +1878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>104</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="89420700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2323,14 +1898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>104</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="91268550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2348,14 +1918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>104</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="91268550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2373,14 +1938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>104</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="91268550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2398,14 +1958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>104</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="91268550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2423,14 +1978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>115</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="96621600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2448,14 +1998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>115</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="96621600"/>
     <ext cx="1409700" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2473,14 +2018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>115</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="96621600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2498,14 +2038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>115</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="96621600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2523,14 +2058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>115</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="98469450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2548,14 +2078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>115</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="98469450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2573,14 +2098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>115</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="98469450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2598,14 +2118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>129</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="106464100"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2623,14 +2138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>129</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="106464100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2648,14 +2158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>129</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="106464100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2673,14 +2178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>129</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="106464100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2698,14 +2198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>129</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="108311950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2723,14 +2218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>129</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="108311950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2748,14 +2238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>129</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="108311950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2773,14 +2258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>140</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="113055400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2798,14 +2278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>140</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="113055400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2823,14 +2298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>140</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="113055400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2848,14 +2318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>140</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="113055400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2873,14 +2338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>140</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="114903250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2898,14 +2358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>140</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="114903250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2923,14 +2378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>140</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="114903250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2948,14 +2398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>151</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="122085100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2973,14 +2418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>151</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="122085100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2998,14 +2438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>151</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="122085100"/>
     <ext cx="1809750" cy="1209675"/>
     <pic>
       <nvPicPr>
@@ -3023,14 +2458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>151</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="122085100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3048,14 +2478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>151</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="123932950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3073,14 +2498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>151</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="123932950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3098,14 +2518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>151</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="123932950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3123,14 +2538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>151</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="123932950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3148,14 +2558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>151</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="125780800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3173,14 +2578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>151</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="125780800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3198,14 +2598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>151</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="125780800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3223,14 +2618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>151</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="125780800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3248,14 +2638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>166</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="133146800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3273,14 +2658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>166</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="133146800"/>
     <ext cx="1809750" cy="533400"/>
     <pic>
       <nvPicPr>
@@ -3298,14 +2678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>166</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="133146800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3323,14 +2698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>166</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="133146800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3348,14 +2718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>166</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="134994650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3373,14 +2738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>166</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="134994650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3398,14 +2758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>166</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="134994650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3423,14 +2778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>166</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="134994650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3448,14 +2798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>177</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="139738100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3473,14 +2818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>177</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="139738100"/>
     <ext cx="1809750" cy="533400"/>
     <pic>
       <nvPicPr>
@@ -3498,14 +2838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>177</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="139738100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3523,14 +2858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>177</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="139738100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3548,14 +2878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>177</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="141585950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3573,14 +2898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>177</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="141585950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3598,14 +2918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>177</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="141585950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3623,14 +2938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>177</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="141585950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3648,14 +2958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>187</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="146329400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3673,14 +2978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>187</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="146329400"/>
     <ext cx="1809750" cy="533400"/>
     <pic>
       <nvPicPr>
@@ -3698,14 +2998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>187</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="146329400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3723,14 +3018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>187</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="146329400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3748,14 +3038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>187</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="148177250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3773,14 +3058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>187</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="148177250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3798,14 +3078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>187</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="148177250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3823,14 +3098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>187</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="148177250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3848,14 +3118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>197</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="153530300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3873,14 +3138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>197</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="153530300"/>
     <ext cx="1809750" cy="533400"/>
     <pic>
       <nvPicPr>
@@ -3898,14 +3158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>197</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="153530300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3923,14 +3178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>197</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="153530300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3948,14 +3198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>197</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="155378150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3973,14 +3218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>197</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="155378150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3998,14 +3238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>197</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="155378150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4023,14 +3258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>197</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="155378150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4048,14 +3278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>208</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="161137600"/>
     <ext cx="1809750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -4073,14 +3298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>208</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="161137600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4098,14 +3318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>208</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="161137600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4123,14 +3338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>208</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="161137600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4148,14 +3358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>208</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="162985450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4173,14 +3378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>208</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="162985450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4198,14 +3398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>208</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="162985450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4223,14 +3418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>218</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="169354500"/>
     <ext cx="1657350" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4248,14 +3438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>218</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="169354500"/>
     <ext cx="1809750" cy="533400"/>
     <pic>
       <nvPicPr>
@@ -4273,14 +3458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>218</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="169354500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4298,14 +3478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>218</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="169354500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4323,14 +3498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>218</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="171202350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4348,14 +3518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>218</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="171202350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4373,14 +3538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>218</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="171202350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4398,14 +3558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>218</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="171202350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4423,14 +3578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>229</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="175945800"/>
     <ext cx="1809750" cy="1419225"/>
     <pic>
       <nvPicPr>
@@ -4448,14 +3598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>229</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="175945800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4473,14 +3618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>229</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="175945800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4498,14 +3638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>229</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="175945800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4523,14 +3658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>229</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="177793650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4548,14 +3678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>229</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="177793650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4573,14 +3698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>229</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="177793650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4598,14 +3718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>229</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="177793650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4623,14 +3738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>229</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="179641500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4648,14 +3758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>229</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="179641500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4673,14 +3778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>240</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="184162700"/>
     <ext cx="1809750" cy="1390650"/>
     <pic>
       <nvPicPr>
@@ -4698,14 +3798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>240</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="184162700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4723,14 +3818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>240</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="184162700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4748,14 +3838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>240</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="184162700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4773,14 +3858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>240</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="186010550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4798,14 +3878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>240</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="186010550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4823,14 +3898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>240</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="186010550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4848,14 +3918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>251</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="194818000"/>
     <ext cx="1809750" cy="1323975"/>
     <pic>
       <nvPicPr>
@@ -4873,14 +3938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>251</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="194818000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4898,14 +3958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>251</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="194818000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4923,14 +3978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>251</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="194818000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4948,14 +3998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>251</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="196665850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4973,14 +4018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>251</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="196665850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4998,14 +4038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>251</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="196665850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5023,14 +4058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>251</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="196665850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5048,14 +4078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>251</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="198513700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5073,14 +4098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>251</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="198513700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5098,14 +4118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>263</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="204457300"/>
     <ext cx="1809750" cy="1419225"/>
     <pic>
       <nvPicPr>
@@ -5123,14 +4138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>263</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="204457300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5148,14 +4158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>263</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="204457300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5173,14 +4178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>263</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="204457300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5198,14 +4198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>263</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="206305150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5223,14 +4218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>263</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="206305150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5248,14 +4238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>263</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="206305150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5273,14 +4258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>263</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="206305150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5298,14 +4278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>263</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="208153000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5323,14 +4298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>263</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="208153000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5348,14 +4318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>276</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="212877400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5373,14 +4338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>276</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="212877400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5398,14 +4358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>276</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="212877400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5423,14 +4378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>276</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="212877400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5448,14 +4398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>276</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="214725250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5473,14 +4418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>276</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="214725250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5498,14 +4438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>288</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="220687900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5523,14 +4458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>288</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="220687900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5548,14 +4478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>288</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="220687900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5573,14 +4498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>288</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="220687900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5598,14 +4518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>288</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="222535750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5623,14 +4538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>288</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="222535750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5648,14 +4558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>288</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="222535750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5673,14 +4578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>300</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="228904800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5698,14 +4598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>300</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="228904800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5723,14 +4618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>300</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="228904800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5748,14 +4638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>300</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="228904800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5773,14 +4658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>300</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="230752650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5798,14 +4678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>300</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="230752650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5823,14 +4698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>300</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="230752650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5848,14 +4718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>311</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="235496100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5873,14 +4738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>311</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="235496100"/>
     <ext cx="1809750" cy="1457325"/>
     <pic>
       <nvPicPr>
@@ -5898,14 +4758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>311</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="235496100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5923,14 +4778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>311</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="235496100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5948,14 +4798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>311</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="237343950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5973,14 +4818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>311</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="237343950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5998,14 +4838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>311</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="237343950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6023,14 +4858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>311</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="237343950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6048,14 +4878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>311</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="239191800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6073,14 +4898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>311</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="239191800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6098,14 +4918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>311</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="239191800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6123,14 +4938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>311</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="239191800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6148,14 +4958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>311</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="241039650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6173,14 +4978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>311</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="241039650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6198,14 +4998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>329</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="254685800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6223,14 +5018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>329</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="254685800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6248,14 +5038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>329</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="254685800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6273,14 +5058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>329</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="254685800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6298,14 +5078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>329</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="256533650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6323,14 +5098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>329</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="256533650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6348,14 +5118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>329</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="256533650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6373,14 +5138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>341</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="261683500"/>
     <ext cx="1809750" cy="1609725"/>
     <pic>
       <nvPicPr>
@@ -6398,14 +5158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>341</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="261683500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6423,14 +5178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>341</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="261683500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6448,14 +5198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>341</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="261683500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6473,14 +5218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>355</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="269494000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6498,14 +5238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>355</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="269494000"/>
     <ext cx="1504950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6523,14 +5258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>355</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="269494000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6548,14 +5278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>355</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="269494000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6573,14 +5298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>355</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="271341850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6598,14 +5318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>355</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="271341850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6623,14 +5338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>355</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="271341850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6648,14 +5358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>355</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="271341850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6673,14 +5378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>355</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="273189700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6698,14 +5398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>365</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="280555700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6723,14 +5418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>365</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="280555700"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -6748,14 +5438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>365</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="280555700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6773,14 +5458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>365</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="280555700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6798,14 +5478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>365</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="282403550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6823,14 +5498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>365</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="282403550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6848,14 +5518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>365</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="282403550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6873,14 +5538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>365</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="282403550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6898,14 +5558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>378</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="293852600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6923,14 +5578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>378</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="293852600"/>
     <ext cx="1647825" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6948,14 +5598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>378</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="293852600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6973,14 +5618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>378</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="293852600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6998,14 +5638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>378</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="295700450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7023,14 +5658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>378</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="295700450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7048,14 +5678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>378</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="295700450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7073,14 +5698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>378</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="295700450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7098,14 +5718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>378</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="297548300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7123,14 +5738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>378</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="297548300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7148,14 +5758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>378</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="297548300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7173,14 +5778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>395</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="308571900"/>
     <ext cx="923925" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7198,14 +5798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>408</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="314172600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -7223,14 +5818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>408</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="314172600"/>
     <ext cx="1809750" cy="1447800"/>
     <pic>
       <nvPicPr>
@@ -7248,14 +5838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>408</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="314172600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7273,14 +5858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>408</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="314172600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7298,14 +5878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>408</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="316020450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7323,14 +5898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>408</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="316020450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7348,14 +5918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>408</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="316020450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7373,14 +5938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>408</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="316020450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7398,14 +5958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>408</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="317868300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7423,14 +5978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>408</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="317868300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7448,14 +5998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>408</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="317868300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7473,14 +6018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>421</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="326859900"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7498,14 +6038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>433</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="334060800"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7523,14 +6058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>443</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="340245700"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7548,7 +6078,7 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
+  </absoluteAnchor>
 </wsDr>
 </file>
 

--- a/카드_아키타입/11_헤어세정.xlsx
+++ b/카드_아키타입/11_헤어세정.xlsx
@@ -200,7 +200,7 @@
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
-    <pos x="6162675" y="0"/>
+    <pos x="7391400" y="0"/>
     <ext cx="1143000" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -220,7 +220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="7404100"/>
+    <pos x="7391400" y="7404100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -240,7 +240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="7404100"/>
+    <pos x="9239250" y="7404100"/>
     <ext cx="1809750" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -260,7 +260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="7404100"/>
+    <pos x="11087100" y="7404100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -280,7 +280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="7404100"/>
+    <pos x="12934950" y="7404100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -300,7 +300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="9251950"/>
+    <pos x="7391400" y="9251950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -320,7 +320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="9251950"/>
+    <pos x="9239250" y="9251950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -340,7 +340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="9251950"/>
+    <pos x="11087100" y="9251950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -360,7 +360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="9251950"/>
+    <pos x="12934950" y="9251950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -380,7 +380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="11099800"/>
+    <pos x="7391400" y="11099800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -400,7 +400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="11099800"/>
+    <pos x="9239250" y="11099800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -420,7 +420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="11099800"/>
+    <pos x="11087100" y="11099800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -440,7 +440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="22123400"/>
+    <pos x="7391400" y="22123400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -460,7 +460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="22123400"/>
+    <pos x="9239250" y="22123400"/>
     <ext cx="1809750" cy="1657350"/>
     <pic>
       <nvPicPr>
@@ -480,7 +480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="22123400"/>
+    <pos x="11087100" y="22123400"/>
     <ext cx="1638300" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -500,7 +500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="38874700"/>
+    <pos x="7391400" y="38874700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -520,7 +520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="38874700"/>
+    <pos x="9239250" y="38874700"/>
     <ext cx="1809750" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -540,7 +540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="38874700"/>
+    <pos x="11087100" y="38874700"/>
     <ext cx="1809750" cy="1028700"/>
     <pic>
       <nvPicPr>
@@ -560,7 +560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="38874700"/>
+    <pos x="12934950" y="38874700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -580,7 +580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="40722550"/>
+    <pos x="7391400" y="40722550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -600,7 +600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="40722550"/>
+    <pos x="9239250" y="40722550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -620,7 +620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="40722550"/>
+    <pos x="11087100" y="40722550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -640,7 +640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="40722550"/>
+    <pos x="12934950" y="40722550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -660,7 +660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="42570400"/>
+    <pos x="7391400" y="42570400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -680,7 +680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="42570400"/>
+    <pos x="9239250" y="42570400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -700,7 +700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="42570400"/>
+    <pos x="11087100" y="42570400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -720,7 +720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="42570400"/>
+    <pos x="12934950" y="42570400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -740,7 +740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="46913800"/>
+    <pos x="7391400" y="46913800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -760,7 +760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="46913800"/>
+    <pos x="9239250" y="46913800"/>
     <ext cx="1809750" cy="1419225"/>
     <pic>
       <nvPicPr>
@@ -780,7 +780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="46913800"/>
+    <pos x="11087100" y="46913800"/>
     <ext cx="1809750" cy="1028700"/>
     <pic>
       <nvPicPr>
@@ -800,7 +800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="46913800"/>
+    <pos x="12934950" y="46913800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -820,7 +820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="48761650"/>
+    <pos x="7391400" y="48761650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -840,7 +840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="48761650"/>
+    <pos x="9239250" y="48761650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -860,7 +860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="48761650"/>
+    <pos x="11087100" y="48761650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -880,7 +880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="48761650"/>
+    <pos x="12934950" y="48761650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -900,7 +900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="50609500"/>
+    <pos x="7391400" y="50609500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -920,7 +920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="50609500"/>
+    <pos x="9239250" y="50609500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -940,7 +940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="50609500"/>
+    <pos x="11087100" y="50609500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -960,7 +960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="50609500"/>
+    <pos x="12934950" y="50609500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -980,7 +980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="58991500"/>
+    <pos x="7391400" y="58991500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1000,7 +1000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="58991500"/>
+    <pos x="9239250" y="58991500"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -1020,7 +1020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="58991500"/>
+    <pos x="11087100" y="58991500"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -1040,7 +1040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="58991500"/>
+    <pos x="12934950" y="58991500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1060,7 +1060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="60839350"/>
+    <pos x="7391400" y="60839350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1080,7 +1080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="60839350"/>
+    <pos x="9239250" y="60839350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1100,7 +1100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="60839350"/>
+    <pos x="11087100" y="60839350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1120,7 +1120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="60839350"/>
+    <pos x="12934950" y="60839350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1140,7 +1140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="62687200"/>
+    <pos x="7391400" y="62687200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1160,7 +1160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="62687200"/>
+    <pos x="9239250" y="62687200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1180,7 +1180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="62687200"/>
+    <pos x="11087100" y="62687200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1200,7 +1200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="62687200"/>
+    <pos x="12934950" y="62687200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1220,7 +1220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="64535050"/>
+    <pos x="7391400" y="64535050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1240,7 +1240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="64535050"/>
+    <pos x="9239250" y="64535050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1260,7 +1260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="64535050"/>
+    <pos x="11087100" y="64535050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1280,7 +1280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="70053200"/>
+    <pos x="7391400" y="70053200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1300,7 +1300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="70053200"/>
+    <pos x="9239250" y="70053200"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1320,7 +1320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="70053200"/>
+    <pos x="11087100" y="70053200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1340,7 +1340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="70053200"/>
+    <pos x="12934950" y="70053200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1360,7 +1360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="71901050"/>
+    <pos x="7391400" y="71901050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1380,7 +1380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="71901050"/>
+    <pos x="9239250" y="71901050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1400,7 +1400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="71901050"/>
+    <pos x="11087100" y="71901050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1420,7 +1420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="71901050"/>
+    <pos x="12934950" y="71901050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1440,7 +1440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="73748900"/>
+    <pos x="7391400" y="73748900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1460,7 +1460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="73748900"/>
+    <pos x="9239250" y="73748900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1480,7 +1480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="73748900"/>
+    <pos x="11087100" y="73748900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1500,7 +1500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="77254100"/>
+    <pos x="7391400" y="77254100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1520,7 +1520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="77254100"/>
+    <pos x="9239250" y="77254100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1540,7 +1540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="77254100"/>
+    <pos x="11087100" y="77254100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1560,7 +1560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="77254100"/>
+    <pos x="12934950" y="77254100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1580,7 +1580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="79101950"/>
+    <pos x="7391400" y="79101950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1600,7 +1600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="79101950"/>
+    <pos x="9239250" y="79101950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1620,7 +1620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="79101950"/>
+    <pos x="11087100" y="79101950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1640,7 +1640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="79101950"/>
+    <pos x="12934950" y="79101950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1660,7 +1660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="83235800"/>
+    <pos x="7391400" y="83235800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1680,7 +1680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="83235800"/>
+    <pos x="9239250" y="83235800"/>
     <ext cx="1514475" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1700,7 +1700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="83235800"/>
+    <pos x="11087100" y="83235800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1720,7 +1720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="83235800"/>
+    <pos x="12934950" y="83235800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1740,7 +1740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="85083650"/>
+    <pos x="7391400" y="85083650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1760,7 +1760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="85083650"/>
+    <pos x="9239250" y="85083650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1780,7 +1780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="85083650"/>
+    <pos x="11087100" y="85083650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1800,7 +1800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="85083650"/>
+    <pos x="12934950" y="85083650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1820,7 +1820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="89420700"/>
+    <pos x="7391400" y="89420700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1840,7 +1840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="89420700"/>
+    <pos x="9239250" y="89420700"/>
     <ext cx="1514475" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1860,7 +1860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="89420700"/>
+    <pos x="11087100" y="89420700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1880,7 +1880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="89420700"/>
+    <pos x="12934950" y="89420700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1900,7 +1900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="91268550"/>
+    <pos x="7391400" y="91268550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1920,7 +1920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="91268550"/>
+    <pos x="9239250" y="91268550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1940,7 +1940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="91268550"/>
+    <pos x="11087100" y="91268550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1960,7 +1960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="91268550"/>
+    <pos x="12934950" y="91268550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1980,7 +1980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="96621600"/>
+    <pos x="7391400" y="96621600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2000,7 +2000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="96621600"/>
+    <pos x="9239250" y="96621600"/>
     <ext cx="1409700" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2020,7 +2020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="96621600"/>
+    <pos x="11087100" y="96621600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2040,7 +2040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="96621600"/>
+    <pos x="12934950" y="96621600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2060,7 +2060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="98469450"/>
+    <pos x="7391400" y="98469450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2080,7 +2080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="98469450"/>
+    <pos x="9239250" y="98469450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2100,7 +2100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="98469450"/>
+    <pos x="11087100" y="98469450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2120,7 +2120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="106464100"/>
+    <pos x="7391400" y="106464100"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2140,7 +2140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="106464100"/>
+    <pos x="9239250" y="106464100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2160,7 +2160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="106464100"/>
+    <pos x="11087100" y="106464100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2180,7 +2180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="106464100"/>
+    <pos x="12934950" y="106464100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2200,7 +2200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="108311950"/>
+    <pos x="7391400" y="108311950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2220,7 +2220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="108311950"/>
+    <pos x="9239250" y="108311950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2240,7 +2240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="108311950"/>
+    <pos x="11087100" y="108311950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2260,7 +2260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="113055400"/>
+    <pos x="7391400" y="113055400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2280,7 +2280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="113055400"/>
+    <pos x="9239250" y="113055400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2300,7 +2300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="113055400"/>
+    <pos x="11087100" y="113055400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2320,7 +2320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="113055400"/>
+    <pos x="12934950" y="113055400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2340,7 +2340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="114903250"/>
+    <pos x="7391400" y="114903250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2360,7 +2360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="114903250"/>
+    <pos x="9239250" y="114903250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2380,7 +2380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="114903250"/>
+    <pos x="11087100" y="114903250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2400,7 +2400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="122085100"/>
+    <pos x="7391400" y="122085100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2420,7 +2420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="122085100"/>
+    <pos x="9239250" y="122085100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2440,7 +2440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="122085100"/>
+    <pos x="11087100" y="122085100"/>
     <ext cx="1809750" cy="1209675"/>
     <pic>
       <nvPicPr>
@@ -2460,7 +2460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="122085100"/>
+    <pos x="12934950" y="122085100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2480,7 +2480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="123932950"/>
+    <pos x="7391400" y="123932950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2500,7 +2500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="123932950"/>
+    <pos x="9239250" y="123932950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2520,7 +2520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="123932950"/>
+    <pos x="11087100" y="123932950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2540,7 +2540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="123932950"/>
+    <pos x="12934950" y="123932950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2560,7 +2560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="125780800"/>
+    <pos x="7391400" y="125780800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2580,7 +2580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="125780800"/>
+    <pos x="9239250" y="125780800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2600,7 +2600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="125780800"/>
+    <pos x="11087100" y="125780800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2620,7 +2620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="125780800"/>
+    <pos x="12934950" y="125780800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2640,7 +2640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="133146800"/>
+    <pos x="7391400" y="133146800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2660,7 +2660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="133146800"/>
+    <pos x="9239250" y="133146800"/>
     <ext cx="1809750" cy="533400"/>
     <pic>
       <nvPicPr>
@@ -2680,7 +2680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="133146800"/>
+    <pos x="11087100" y="133146800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2700,7 +2700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="133146800"/>
+    <pos x="12934950" y="133146800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2720,7 +2720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="134994650"/>
+    <pos x="7391400" y="134994650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2740,7 +2740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="134994650"/>
+    <pos x="9239250" y="134994650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2760,7 +2760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="134994650"/>
+    <pos x="11087100" y="134994650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2780,7 +2780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="134994650"/>
+    <pos x="12934950" y="134994650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2800,7 +2800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="139738100"/>
+    <pos x="7391400" y="139738100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2820,7 +2820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="139738100"/>
+    <pos x="9239250" y="139738100"/>
     <ext cx="1809750" cy="533400"/>
     <pic>
       <nvPicPr>
@@ -2840,7 +2840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="139738100"/>
+    <pos x="11087100" y="139738100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2860,7 +2860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="139738100"/>
+    <pos x="12934950" y="139738100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2880,7 +2880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="141585950"/>
+    <pos x="7391400" y="141585950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2900,7 +2900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="141585950"/>
+    <pos x="9239250" y="141585950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2920,7 +2920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="141585950"/>
+    <pos x="11087100" y="141585950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2940,7 +2940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="141585950"/>
+    <pos x="12934950" y="141585950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2960,7 +2960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="146329400"/>
+    <pos x="7391400" y="146329400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2980,7 +2980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="146329400"/>
+    <pos x="9239250" y="146329400"/>
     <ext cx="1809750" cy="533400"/>
     <pic>
       <nvPicPr>
@@ -3000,7 +3000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="146329400"/>
+    <pos x="11087100" y="146329400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3020,7 +3020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="146329400"/>
+    <pos x="12934950" y="146329400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3040,7 +3040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="148177250"/>
+    <pos x="7391400" y="148177250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3060,7 +3060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="148177250"/>
+    <pos x="9239250" y="148177250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3080,7 +3080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="148177250"/>
+    <pos x="11087100" y="148177250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3100,7 +3100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="148177250"/>
+    <pos x="12934950" y="148177250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3120,7 +3120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="153530300"/>
+    <pos x="7391400" y="153530300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3140,7 +3140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="153530300"/>
+    <pos x="9239250" y="153530300"/>
     <ext cx="1809750" cy="533400"/>
     <pic>
       <nvPicPr>
@@ -3160,7 +3160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="153530300"/>
+    <pos x="11087100" y="153530300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3180,7 +3180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="153530300"/>
+    <pos x="12934950" y="153530300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3200,7 +3200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="155378150"/>
+    <pos x="7391400" y="155378150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3220,7 +3220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="155378150"/>
+    <pos x="9239250" y="155378150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3240,7 +3240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="155378150"/>
+    <pos x="11087100" y="155378150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3260,7 +3260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="155378150"/>
+    <pos x="12934950" y="155378150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3280,7 +3280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="161137600"/>
+    <pos x="7391400" y="161137600"/>
     <ext cx="1809750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -3300,7 +3300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="161137600"/>
+    <pos x="9239250" y="161137600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3320,7 +3320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="161137600"/>
+    <pos x="11087100" y="161137600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3340,7 +3340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="161137600"/>
+    <pos x="12934950" y="161137600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3360,7 +3360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="162985450"/>
+    <pos x="7391400" y="162985450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3380,7 +3380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="162985450"/>
+    <pos x="9239250" y="162985450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3400,7 +3400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="162985450"/>
+    <pos x="11087100" y="162985450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3420,7 +3420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="169354500"/>
+    <pos x="7391400" y="169354500"/>
     <ext cx="1657350" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3440,7 +3440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="169354500"/>
+    <pos x="9239250" y="169354500"/>
     <ext cx="1809750" cy="533400"/>
     <pic>
       <nvPicPr>
@@ -3460,7 +3460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="169354500"/>
+    <pos x="11087100" y="169354500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3480,7 +3480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="169354500"/>
+    <pos x="12934950" y="169354500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3500,7 +3500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="171202350"/>
+    <pos x="7391400" y="171202350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3520,7 +3520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="171202350"/>
+    <pos x="9239250" y="171202350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3540,7 +3540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="171202350"/>
+    <pos x="11087100" y="171202350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3560,7 +3560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="171202350"/>
+    <pos x="12934950" y="171202350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3580,7 +3580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="175945800"/>
+    <pos x="7391400" y="175945800"/>
     <ext cx="1809750" cy="1419225"/>
     <pic>
       <nvPicPr>
@@ -3600,7 +3600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="175945800"/>
+    <pos x="9239250" y="175945800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3620,7 +3620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="175945800"/>
+    <pos x="11087100" y="175945800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3640,7 +3640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="175945800"/>
+    <pos x="12934950" y="175945800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3660,7 +3660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="177793650"/>
+    <pos x="7391400" y="177793650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3680,7 +3680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="177793650"/>
+    <pos x="9239250" y="177793650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3700,7 +3700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="177793650"/>
+    <pos x="11087100" y="177793650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3720,7 +3720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="177793650"/>
+    <pos x="12934950" y="177793650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3740,7 +3740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="179641500"/>
+    <pos x="7391400" y="179641500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3760,7 +3760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="179641500"/>
+    <pos x="9239250" y="179641500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3780,7 +3780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="184162700"/>
+    <pos x="7391400" y="184162700"/>
     <ext cx="1809750" cy="1390650"/>
     <pic>
       <nvPicPr>
@@ -3800,7 +3800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="184162700"/>
+    <pos x="9239250" y="184162700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3820,7 +3820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="184162700"/>
+    <pos x="11087100" y="184162700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3840,7 +3840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="184162700"/>
+    <pos x="12934950" y="184162700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3860,7 +3860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="186010550"/>
+    <pos x="7391400" y="186010550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3880,7 +3880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="186010550"/>
+    <pos x="9239250" y="186010550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3900,7 +3900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="186010550"/>
+    <pos x="11087100" y="186010550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3920,7 +3920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="194818000"/>
+    <pos x="7391400" y="194818000"/>
     <ext cx="1809750" cy="1323975"/>
     <pic>
       <nvPicPr>
@@ -3940,7 +3940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="194818000"/>
+    <pos x="9239250" y="194818000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3960,7 +3960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="194818000"/>
+    <pos x="11087100" y="194818000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3980,7 +3980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="194818000"/>
+    <pos x="12934950" y="194818000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4000,7 +4000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="196665850"/>
+    <pos x="7391400" y="196665850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4020,7 +4020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="196665850"/>
+    <pos x="9239250" y="196665850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4040,7 +4040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="196665850"/>
+    <pos x="11087100" y="196665850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4060,7 +4060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="196665850"/>
+    <pos x="12934950" y="196665850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4080,7 +4080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="198513700"/>
+    <pos x="7391400" y="198513700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4100,7 +4100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="198513700"/>
+    <pos x="9239250" y="198513700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4120,7 +4120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="204457300"/>
+    <pos x="7391400" y="204457300"/>
     <ext cx="1809750" cy="1419225"/>
     <pic>
       <nvPicPr>
@@ -4140,7 +4140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="204457300"/>
+    <pos x="9239250" y="204457300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4160,7 +4160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="204457300"/>
+    <pos x="11087100" y="204457300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4180,7 +4180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="204457300"/>
+    <pos x="12934950" y="204457300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4200,7 +4200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="206305150"/>
+    <pos x="7391400" y="206305150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4220,7 +4220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="206305150"/>
+    <pos x="9239250" y="206305150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4240,7 +4240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="206305150"/>
+    <pos x="11087100" y="206305150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4260,7 +4260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="206305150"/>
+    <pos x="12934950" y="206305150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4280,7 +4280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="208153000"/>
+    <pos x="7391400" y="208153000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4300,7 +4300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="208153000"/>
+    <pos x="9239250" y="208153000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4320,7 +4320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="212877400"/>
+    <pos x="7391400" y="212877400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4340,7 +4340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="212877400"/>
+    <pos x="9239250" y="212877400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4360,7 +4360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="212877400"/>
+    <pos x="11087100" y="212877400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4380,7 +4380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="212877400"/>
+    <pos x="12934950" y="212877400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4400,7 +4400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="214725250"/>
+    <pos x="7391400" y="214725250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4420,7 +4420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="214725250"/>
+    <pos x="9239250" y="214725250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4440,7 +4440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="220687900"/>
+    <pos x="7391400" y="220687900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4460,7 +4460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="220687900"/>
+    <pos x="9239250" y="220687900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4480,7 +4480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="220687900"/>
+    <pos x="11087100" y="220687900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4500,7 +4500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="220687900"/>
+    <pos x="12934950" y="220687900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4520,7 +4520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="222535750"/>
+    <pos x="7391400" y="222535750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4540,7 +4540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="222535750"/>
+    <pos x="9239250" y="222535750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4560,7 +4560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="222535750"/>
+    <pos x="11087100" y="222535750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4580,7 +4580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="228904800"/>
+    <pos x="7391400" y="228904800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4600,7 +4600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="228904800"/>
+    <pos x="9239250" y="228904800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4620,7 +4620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="228904800"/>
+    <pos x="11087100" y="228904800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4640,7 +4640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="228904800"/>
+    <pos x="12934950" y="228904800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4660,7 +4660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="230752650"/>
+    <pos x="7391400" y="230752650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4680,7 +4680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="230752650"/>
+    <pos x="9239250" y="230752650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4700,7 +4700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="230752650"/>
+    <pos x="11087100" y="230752650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4720,7 +4720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="235496100"/>
+    <pos x="7391400" y="235496100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4740,7 +4740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="235496100"/>
+    <pos x="9239250" y="235496100"/>
     <ext cx="1809750" cy="1457325"/>
     <pic>
       <nvPicPr>
@@ -4760,7 +4760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="235496100"/>
+    <pos x="11087100" y="235496100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4780,7 +4780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="235496100"/>
+    <pos x="12934950" y="235496100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4800,7 +4800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="237343950"/>
+    <pos x="7391400" y="237343950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4820,7 +4820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="237343950"/>
+    <pos x="9239250" y="237343950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4840,7 +4840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="237343950"/>
+    <pos x="11087100" y="237343950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4860,7 +4860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="237343950"/>
+    <pos x="12934950" y="237343950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4880,7 +4880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="239191800"/>
+    <pos x="7391400" y="239191800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4900,7 +4900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="239191800"/>
+    <pos x="9239250" y="239191800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4920,7 +4920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="239191800"/>
+    <pos x="11087100" y="239191800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4940,7 +4940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="239191800"/>
+    <pos x="12934950" y="239191800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4960,7 +4960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="241039650"/>
+    <pos x="7391400" y="241039650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4980,7 +4980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="241039650"/>
+    <pos x="9239250" y="241039650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5000,7 +5000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="254685800"/>
+    <pos x="7391400" y="254685800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5020,7 +5020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="254685800"/>
+    <pos x="9239250" y="254685800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5040,7 +5040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="254685800"/>
+    <pos x="11087100" y="254685800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5060,7 +5060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="254685800"/>
+    <pos x="12934950" y="254685800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5080,7 +5080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="256533650"/>
+    <pos x="7391400" y="256533650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5100,7 +5100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="256533650"/>
+    <pos x="9239250" y="256533650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5120,7 +5120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="256533650"/>
+    <pos x="11087100" y="256533650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5140,7 +5140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="261683500"/>
+    <pos x="7391400" y="261683500"/>
     <ext cx="1809750" cy="1609725"/>
     <pic>
       <nvPicPr>
@@ -5160,7 +5160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="261683500"/>
+    <pos x="9239250" y="261683500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5180,7 +5180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="261683500"/>
+    <pos x="11087100" y="261683500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5200,7 +5200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="261683500"/>
+    <pos x="12934950" y="261683500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5220,7 +5220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="269494000"/>
+    <pos x="7391400" y="269494000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5240,7 +5240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="269494000"/>
+    <pos x="9239250" y="269494000"/>
     <ext cx="1504950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5260,7 +5260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="269494000"/>
+    <pos x="11087100" y="269494000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5280,7 +5280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="269494000"/>
+    <pos x="12934950" y="269494000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5300,7 +5300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="271341850"/>
+    <pos x="7391400" y="271341850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5320,7 +5320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="271341850"/>
+    <pos x="9239250" y="271341850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5340,7 +5340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="271341850"/>
+    <pos x="11087100" y="271341850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5360,7 +5360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="271341850"/>
+    <pos x="12934950" y="271341850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5380,7 +5380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="273189700"/>
+    <pos x="7391400" y="273189700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5400,7 +5400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="280555700"/>
+    <pos x="7391400" y="280555700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5420,7 +5420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="280555700"/>
+    <pos x="9239250" y="280555700"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -5440,7 +5440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="280555700"/>
+    <pos x="11087100" y="280555700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5460,7 +5460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="280555700"/>
+    <pos x="12934950" y="280555700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5480,7 +5480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="282403550"/>
+    <pos x="7391400" y="282403550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5500,7 +5500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="282403550"/>
+    <pos x="9239250" y="282403550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5520,7 +5520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="282403550"/>
+    <pos x="11087100" y="282403550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5540,7 +5540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="282403550"/>
+    <pos x="12934950" y="282403550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5560,7 +5560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="293852600"/>
+    <pos x="7391400" y="293852600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5580,7 +5580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="293852600"/>
+    <pos x="9239250" y="293852600"/>
     <ext cx="1647825" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5600,7 +5600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="293852600"/>
+    <pos x="11087100" y="293852600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5620,7 +5620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="293852600"/>
+    <pos x="12934950" y="293852600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5640,7 +5640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="295700450"/>
+    <pos x="7391400" y="295700450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5660,7 +5660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="295700450"/>
+    <pos x="9239250" y="295700450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5680,7 +5680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="295700450"/>
+    <pos x="11087100" y="295700450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5700,7 +5700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="295700450"/>
+    <pos x="12934950" y="295700450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5720,7 +5720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="297548300"/>
+    <pos x="7391400" y="297548300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5740,7 +5740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="297548300"/>
+    <pos x="9239250" y="297548300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5760,7 +5760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="297548300"/>
+    <pos x="11087100" y="297548300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5780,7 +5780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="308571900"/>
+    <pos x="7391400" y="308571900"/>
     <ext cx="923925" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5800,7 +5800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="314172600"/>
+    <pos x="7391400" y="314172600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5820,7 +5820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="314172600"/>
+    <pos x="9239250" y="314172600"/>
     <ext cx="1809750" cy="1447800"/>
     <pic>
       <nvPicPr>
@@ -5840,7 +5840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="314172600"/>
+    <pos x="11087100" y="314172600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5860,7 +5860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="314172600"/>
+    <pos x="12934950" y="314172600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5880,7 +5880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="316020450"/>
+    <pos x="7391400" y="316020450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5900,7 +5900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="316020450"/>
+    <pos x="9239250" y="316020450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5920,7 +5920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="316020450"/>
+    <pos x="11087100" y="316020450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5940,7 +5940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="316020450"/>
+    <pos x="12934950" y="316020450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5960,7 +5960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="317868300"/>
+    <pos x="7391400" y="317868300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5980,7 +5980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="317868300"/>
+    <pos x="9239250" y="317868300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6000,7 +6000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="317868300"/>
+    <pos x="11087100" y="317868300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6020,7 +6020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="326859900"/>
+    <pos x="7391400" y="326859900"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6040,7 +6040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="334060800"/>
+    <pos x="7391400" y="334060800"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6060,7 +6060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="340245700"/>
+    <pos x="7391400" y="340245700"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6378,7 +6378,7 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="2" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">

--- a/카드_아키타입/11_헤어세정.xlsx
+++ b/카드_아키타입/11_헤어세정.xlsx
@@ -3420,7 +3420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="171081700"/>
+    <pos x="7848600" y="170878500"/>
     <ext cx="1809750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -3440,7 +3440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="171081700"/>
+    <pos x="9696450" y="170878500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3460,7 +3460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="171081700"/>
+    <pos x="11544300" y="170878500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3480,7 +3480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="171081700"/>
+    <pos x="13392150" y="170878500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3500,7 +3500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="172929550"/>
+    <pos x="7848600" y="172726350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3520,7 +3520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="172929550"/>
+    <pos x="9696450" y="172726350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3540,7 +3540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="172929550"/>
+    <pos x="11544300" y="172726350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3560,7 +3560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="179476400"/>
+    <pos x="7848600" y="179273200"/>
     <ext cx="1657350" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3580,7 +3580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="179476400"/>
+    <pos x="9696450" y="179273200"/>
     <ext cx="1809750" cy="533400"/>
     <pic>
       <nvPicPr>
@@ -3600,7 +3600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="179476400"/>
+    <pos x="11544300" y="179273200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3620,7 +3620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="179476400"/>
+    <pos x="13392150" y="179273200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3640,7 +3640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="181324250"/>
+    <pos x="7848600" y="181121050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3660,7 +3660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="181324250"/>
+    <pos x="9696450" y="181121050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3680,7 +3680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="181324250"/>
+    <pos x="11544300" y="181121050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3700,7 +3700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="181324250"/>
+    <pos x="13392150" y="181121050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3720,7 +3720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="186651900"/>
+    <pos x="7848600" y="186448700"/>
     <ext cx="1809750" cy="1419225"/>
     <pic>
       <nvPicPr>
@@ -3740,7 +3740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="186651900"/>
+    <pos x="9696450" y="186448700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3760,7 +3760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="186651900"/>
+    <pos x="11544300" y="186448700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3780,7 +3780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="186651900"/>
+    <pos x="13392150" y="186448700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3800,7 +3800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="188499750"/>
+    <pos x="7848600" y="188296550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3820,7 +3820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="188499750"/>
+    <pos x="9696450" y="188296550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3840,7 +3840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="188499750"/>
+    <pos x="11544300" y="188296550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3860,7 +3860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="188499750"/>
+    <pos x="13392150" y="188296550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3880,7 +3880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="190347600"/>
+    <pos x="7848600" y="190144400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3900,7 +3900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="190347600"/>
+    <pos x="9696450" y="190144400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3920,7 +3920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="195453000"/>
+    <pos x="7848600" y="195249800"/>
     <ext cx="1809750" cy="1390650"/>
     <pic>
       <nvPicPr>
@@ -3940,7 +3940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="195453000"/>
+    <pos x="9696450" y="195249800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3960,7 +3960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="195453000"/>
+    <pos x="11544300" y="195249800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3980,7 +3980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="195453000"/>
+    <pos x="13392150" y="195249800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4000,7 +4000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="197300850"/>
+    <pos x="7848600" y="197097650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4020,7 +4020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="197300850"/>
+    <pos x="9696450" y="197097650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4040,7 +4040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="197300850"/>
+    <pos x="11544300" y="197097650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4060,7 +4060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="206692500"/>
+    <pos x="7848600" y="206489300"/>
     <ext cx="1809750" cy="1323975"/>
     <pic>
       <nvPicPr>
@@ -4080,7 +4080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="206692500"/>
+    <pos x="9696450" y="206489300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4100,7 +4100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="206692500"/>
+    <pos x="11544300" y="206489300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4120,7 +4120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="206692500"/>
+    <pos x="13392150" y="206489300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4140,7 +4140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="208540350"/>
+    <pos x="7848600" y="208337150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4160,7 +4160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="208540350"/>
+    <pos x="9696450" y="208337150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4180,7 +4180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="208540350"/>
+    <pos x="11544300" y="208337150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4200,7 +4200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="208540350"/>
+    <pos x="13392150" y="208337150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4220,7 +4220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="210388200"/>
+    <pos x="7848600" y="210185000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4240,7 +4240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="210388200"/>
+    <pos x="9696450" y="210185000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4260,7 +4260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="217119200"/>
+    <pos x="7848600" y="216916000"/>
     <ext cx="1809750" cy="1419225"/>
     <pic>
       <nvPicPr>
@@ -4280,7 +4280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="217119200"/>
+    <pos x="9696450" y="216916000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4300,7 +4300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="217119200"/>
+    <pos x="11544300" y="216916000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4320,7 +4320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="217119200"/>
+    <pos x="13392150" y="216916000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4340,7 +4340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="218967050"/>
+    <pos x="7848600" y="218763850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4360,7 +4360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="218967050"/>
+    <pos x="9696450" y="218763850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4380,7 +4380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="218967050"/>
+    <pos x="11544300" y="218763850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4400,7 +4400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="218967050"/>
+    <pos x="13392150" y="218763850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4420,7 +4420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="220814900"/>
+    <pos x="7848600" y="220611700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4440,7 +4440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="220814900"/>
+    <pos x="9696450" y="220611700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4460,7 +4460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="225920300"/>
+    <pos x="7848600" y="225717100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4480,7 +4480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="225920300"/>
+    <pos x="9696450" y="225717100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4500,7 +4500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="225920300"/>
+    <pos x="11544300" y="225717100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4520,7 +4520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="225920300"/>
+    <pos x="13392150" y="225717100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4540,7 +4540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="227768150"/>
+    <pos x="7848600" y="227564950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4560,7 +4560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="227768150"/>
+    <pos x="9696450" y="227564950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4580,7 +4580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="233705400"/>
+    <pos x="7848600" y="233502200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4600,7 +4600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="233705400"/>
+    <pos x="9696450" y="233502200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4620,7 +4620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="233705400"/>
+    <pos x="11544300" y="233502200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4640,7 +4640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="233705400"/>
+    <pos x="13392150" y="233502200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4660,7 +4660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="235553250"/>
+    <pos x="7848600" y="235350050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4680,7 +4680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="235553250"/>
+    <pos x="9696450" y="235350050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4700,7 +4700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="235553250"/>
+    <pos x="11544300" y="235350050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4720,7 +4720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="242303300"/>
+    <pos x="7848600" y="242100100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4740,7 +4740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="242303300"/>
+    <pos x="9696450" y="242100100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4760,7 +4760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="242303300"/>
+    <pos x="11544300" y="242100100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4780,7 +4780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="242303300"/>
+    <pos x="13392150" y="242100100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4800,7 +4800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="244151150"/>
+    <pos x="7848600" y="243947950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4820,7 +4820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="244151150"/>
+    <pos x="9696450" y="243947950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4840,7 +4840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="244151150"/>
+    <pos x="11544300" y="243947950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4860,7 +4860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="249275600"/>
+    <pos x="7848600" y="249072400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4880,7 +4880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="249275600"/>
+    <pos x="9696450" y="249072400"/>
     <ext cx="1809750" cy="1457325"/>
     <pic>
       <nvPicPr>
@@ -4900,7 +4900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="249275600"/>
+    <pos x="11544300" y="249072400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4920,7 +4920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="249275600"/>
+    <pos x="13392150" y="249072400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4940,7 +4940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="251123450"/>
+    <pos x="7848600" y="250920250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4960,7 +4960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="251123450"/>
+    <pos x="9696450" y="250920250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4980,7 +4980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="251123450"/>
+    <pos x="11544300" y="250920250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5000,7 +5000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="251123450"/>
+    <pos x="13392150" y="250920250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5020,7 +5020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="252971300"/>
+    <pos x="7848600" y="252768100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5040,7 +5040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="252971300"/>
+    <pos x="9696450" y="252768100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5060,7 +5060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="252971300"/>
+    <pos x="11544300" y="252768100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5080,7 +5080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="252971300"/>
+    <pos x="13392150" y="252768100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5100,7 +5100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="254819150"/>
+    <pos x="7848600" y="254615950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5120,7 +5120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="254819150"/>
+    <pos x="9696450" y="254615950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5140,7 +5140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="268643100"/>
+    <pos x="7848600" y="268236700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5160,7 +5160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="268643100"/>
+    <pos x="9696450" y="268236700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5180,7 +5180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="268643100"/>
+    <pos x="11544300" y="268236700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5200,7 +5200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="268643100"/>
+    <pos x="13392150" y="268236700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5220,7 +5220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="270490950"/>
+    <pos x="7848600" y="270084550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5240,7 +5240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="270490950"/>
+    <pos x="9696450" y="270084550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5260,7 +5260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="270490950"/>
+    <pos x="11544300" y="270084550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5280,7 +5280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="276225000"/>
+    <pos x="7848600" y="275818600"/>
     <ext cx="1809750" cy="1609725"/>
     <pic>
       <nvPicPr>
@@ -5300,7 +5300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="276225000"/>
+    <pos x="9696450" y="275818600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5320,7 +5320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="276225000"/>
+    <pos x="11544300" y="275818600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5340,7 +5340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="276225000"/>
+    <pos x="13392150" y="275818600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5360,7 +5360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="284822900"/>
+    <pos x="7848600" y="284416500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5380,7 +5380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="284822900"/>
+    <pos x="9696450" y="284416500"/>
     <ext cx="1504950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5400,7 +5400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="284822900"/>
+    <pos x="11544300" y="284416500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5420,7 +5420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="284822900"/>
+    <pos x="13392150" y="284416500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5440,7 +5440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="286670750"/>
+    <pos x="7848600" y="286264350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5460,7 +5460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="286670750"/>
+    <pos x="9696450" y="286264350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5480,7 +5480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="286670750"/>
+    <pos x="11544300" y="286264350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5500,7 +5500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="286670750"/>
+    <pos x="13392150" y="286264350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5520,7 +5520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="288518600"/>
+    <pos x="7848600" y="288112200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5540,7 +5540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="296062400"/>
+    <pos x="7848600" y="295656000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5560,7 +5560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="296062400"/>
+    <pos x="9696450" y="295656000"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -5580,7 +5580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="296062400"/>
+    <pos x="11544300" y="295656000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5600,7 +5600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="296062400"/>
+    <pos x="13392150" y="295656000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5620,7 +5620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="297910250"/>
+    <pos x="7848600" y="297503850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5640,7 +5640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="297910250"/>
+    <pos x="9696450" y="297503850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5660,7 +5660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="297910250"/>
+    <pos x="11544300" y="297503850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5680,7 +5680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="297910250"/>
+    <pos x="13392150" y="297503850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5700,7 +5700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="310553100"/>
+    <pos x="7848600" y="310146700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5720,7 +5720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="310553100"/>
+    <pos x="9696450" y="310146700"/>
     <ext cx="1647825" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5740,7 +5740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="310553100"/>
+    <pos x="11544300" y="310146700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5760,7 +5760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="310553100"/>
+    <pos x="13392150" y="310146700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5780,7 +5780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="312400950"/>
+    <pos x="7848600" y="311994550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5800,7 +5800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="312400950"/>
+    <pos x="9696450" y="311994550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5820,7 +5820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="312400950"/>
+    <pos x="11544300" y="311994550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5840,7 +5840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="312400950"/>
+    <pos x="13392150" y="311994550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5860,7 +5860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="314248800"/>
+    <pos x="7848600" y="313842399"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5880,7 +5880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="314248800"/>
+    <pos x="9696450" y="313842399"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5900,7 +5900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="314248800"/>
+    <pos x="11544300" y="313842399"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5920,7 +5920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="325856600"/>
+    <pos x="7848600" y="325450200"/>
     <ext cx="923925" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5940,7 +5940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="331863700"/>
+    <pos x="7848600" y="331457300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5960,7 +5960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="331863700"/>
+    <pos x="9696450" y="331457300"/>
     <ext cx="1809750" cy="1447800"/>
     <pic>
       <nvPicPr>
@@ -5980,7 +5980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="331863700"/>
+    <pos x="11544300" y="331457300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6000,7 +6000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="331863700"/>
+    <pos x="13392150" y="331457300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6020,7 +6020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="333711550"/>
+    <pos x="7848600" y="333305150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6040,7 +6040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="333711550"/>
+    <pos x="9696450" y="333305150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6060,7 +6060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="333711550"/>
+    <pos x="11544300" y="333305150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6080,7 +6080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="333711550"/>
+    <pos x="13392150" y="333305150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6100,7 +6100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="335559400"/>
+    <pos x="7848600" y="335153000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6120,7 +6120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="335559400"/>
+    <pos x="9696450" y="335153000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6140,7 +6140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="335559400"/>
+    <pos x="11544300" y="335153000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6160,7 +6160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="345135200"/>
+    <pos x="7848600" y="344728800"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6180,7 +6180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="352336100"/>
+    <pos x="7848600" y="351929700"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6200,7 +6200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="358521000"/>
+    <pos x="7848600" y="358114600"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6669,7 +6669,7 @@
           <t>하수오 추출, 모발·두피 강화(전통 백모 케어)</t>
         </is>
       </c>
-      <c r="F9" s="10" t="n"/>
+      <c r="F9" s="10" t="inlineStr"/>
     </row>
     <row r="10" ht="80" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제는 생약 중 항균력이 우수한 오배자, 가자, 석곡, 산초를 초음파 방식으로 / 추출하여 조합한 화장품용 천연유래 항균제입니다</t>
+          <t>천연한방보존제는 생약 중 항균력이 우수한 오배자, 가자, 석곡, 산초를 초음파 방식으로 · 추출하여 조합한 화장품용 천연유래 항균제입니다</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올0.6g / (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
+          <t>1,2-헥산디올0.6g · (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -6815,10 +6815,10 @@
       </c>
       <c r="E18" s="18" t="inlineStr">
         <is>
-          <t>7가지 한방샴푸레시피를 기반으로 만들어짐. / 사용하기 쉽게 만든 배합하여 만든 / 순한 샴푸베이스. / 라벤더꽃수, LES, 코카미도프로필베타인, 폴리쿼터, 글루카메이트, 정제수 등등의 성분을 활용한 최적의 배합.</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="n"/>
+          <t>7가지 한방샴푸레시피를 기반으로 만들어짐. · 사용하기 쉽게 만든 배합하여 만든 · 순한 샴푸베이스. · 라벤더꽃수, LES, 코카미도프로필베타인, 폴리쿼터, 글루카메이트, 정제수 등등의 성분을 활용한 최적의 배합.</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="inlineStr"/>
     </row>
     <row r="19" ht="80" customHeight="1">
       <c r="A19" s="18" t="inlineStr">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="E19" s="18" t="inlineStr">
         <is>
-          <t>거제산 생알로에잎을 껍질제거한 후 갈아만듬. / 남은 재료 활용 팁 : 젤타입스킨으로 사용가능, / 헤어에센스로 사용가능.</t>
+          <t>거제산 생알로에잎을 껍질제거한 후 갈아만듬. · 남은 재료 활용 팁 : 젤타입스킨으로 사용가능 · 헤어에센스로 사용가능.</t>
         </is>
       </c>
       <c r="F19" s="18" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="E20" s="18" t="inlineStr">
         <is>
-          <t>USDA Organic 유기농 인증 / 유기농 두피진정, 튼튼에 좋은 5가지 허브 / (라벤더꽃, 캐모마일꽃, 병풀, 녹차, 알로에잎)추출물, 유기농 글리세린베이스</t>
+          <t>USDA Organic 유기농 인증 · 유기농 두피진정, 튼튼에 좋은 5가지 허브 · (라벤더꽃, 캐모마일꽃, 병풀, 녹차, 알로에잎)추출물, 유기농 글리세린베이스</t>
         </is>
       </c>
       <c r="F20" s="18" t="inlineStr">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="E23" s="18" t="inlineStr">
         <is>
-          <t>장미향이 나는 나무 심지에서 추출, / 베이스노트, 모든 피부, 아로마테라피</t>
+          <t>장미향이 나는 나무 심지에서 추출 · 베이스노트, 모든 피부, 아로마테라피</t>
         </is>
       </c>
       <c r="F23" s="18" t="inlineStr">
@@ -7159,10 +7159,10 @@
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>기존 7가지 한방샴푸레시피를 / 기반으로 만들어짐. / 사용하기 쉽게 세정, 점도 등에 관련된 / 재료를 배합하여 만든 순한 샴푸베이스. / 라벤더꽃수, LES, 코카미도프로필베타인, 폴리쿼터, 글루카메이트, 정제수 등등의 성분을 활용한 최적의 배합.</t>
-        </is>
-      </c>
-      <c r="F33" s="10" t="n"/>
+          <t>기존 7가지 한방샴푸레시피를 · 기반으로 만들어짐. · 사용하기 쉽게 세정, 점도 등에 관련된 · 재료를 배합하여 만든 순한 샴푸베이스. · 라벤더꽃수, LES, 코카미도프로필베타인, 폴리쿼터, 글루카메이트, 정제수 등등의 성분을 활용한 최적의 배합.</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr"/>
     </row>
     <row r="34" ht="96" customHeight="1">
       <c r="A34" s="10" t="inlineStr">
@@ -7187,10 +7187,10 @@
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>7가지한약재(박하, 적하수오, 약쑥, 감초, 삼백초,측백,당귀)를 진공감압추출기를 / 이용해 저온에서 추출. / 유효성분을 최대한 보존하면서 제조. / 시간 절약.</t>
-        </is>
-      </c>
-      <c r="F34" s="10" t="n"/>
+          <t>7가지한약재(박하, 적하수오, 약쑥, 감초, 삼백초,측백,당귀)를 진공감압추출기를 · 이용해 저온에서 추출. · 유효성분을 최대한 보존하면서 제조. · 시간 절약.</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr"/>
     </row>
     <row r="35" ht="64" customHeight="1">
       <c r="A35" s="10" t="inlineStr">
@@ -7247,12 +7247,12 @@
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>시더우드EO, 레몬글라스EO, 페파민트EO, 라벤더EO 등 / 비듬, 지루성 두피관리에 사용</t>
+          <t>시더우드EO, 레몬글라스EO, 페파민트EO, 라벤더EO 등 · 비듬, 지루성 두피관리에 사용</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>시더우드 / 에센셜오일, / 민트쿨 컴플렉스 / 블랜딩오일</t>
+          <t>시더우드 · 에센셜오일 · 민트쿨 컴플렉스 · 블랜딩오일</t>
         </is>
       </c>
     </row>
@@ -7441,10 +7441,10 @@
       </c>
       <c r="E47" s="18" t="inlineStr">
         <is>
-          <t>이미 만들어진 물비누, / 자체점도가 있고 거품, / 세정효과, 보습, 보존제포함</t>
-        </is>
-      </c>
-      <c r="F47" s="18" t="n"/>
+          <t>이미 만들어진 물비누 · 자체점도가 있고 거품 · 세정효과, 보습, 보존제포함</t>
+        </is>
+      </c>
+      <c r="F47" s="18" t="inlineStr"/>
     </row>
     <row r="48" ht="80" customHeight="1">
       <c r="A48" s="18" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="E48" s="18" t="inlineStr">
         <is>
-          <t>보성 무농약 녹차, / 식물성 에탄올에 저온추출, 감압농축, 동결건조하여 유효성분을 많이 포함하고 있습니다. 폴리페놀 함량이 3배높고 항산화 작용</t>
+          <t>보성 무농약 녹차 · 식물성 에탄올에 저온추출, 감압농축, 동결건조하여 유효성분을 많이 포함하고 있습니다. 폴리페놀 함량이 3배높고 항산화 작용</t>
         </is>
       </c>
       <c r="F48" s="18" t="inlineStr">
         <is>
-          <t>녹소초 추출물, / 유기농 브라이트닝 5 등.</t>
+          <t>녹소초 추출물 · 유기농 브라이트닝 5 등.</t>
         </is>
       </c>
     </row>
@@ -7533,12 +7533,12 @@
       </c>
       <c r="E50" s="18" t="inlineStr">
         <is>
-          <t>샴푸베이스에 이미 있지만 추가 보습을 원하면 모발 보습제로 넣어주세요. / 모발, 두피 보습제, / 좀더 모발을 부드럽게, 많은 양을 넣을 경우 점도가 묽어짐.</t>
+          <t>샴푸베이스에 이미 있지만 추가 보습을 원하면 모발 보습제로 넣어주세요. · 모발, 두피 보습제 · 좀더 모발을 부드럽게, 많은 양을 넣을 경우 점도가 묽어짐.</t>
         </is>
       </c>
       <c r="F50" s="18" t="inlineStr">
         <is>
-          <t>다중)히아루론산, 에코보습제 / 글리세린 등</t>
+          <t>다중)히아루론산, 에코보습제 · 글리세린 등</t>
         </is>
       </c>
     </row>
@@ -7693,10 +7693,10 @@
       </c>
       <c r="E58" s="10" t="inlineStr">
         <is>
-          <t>이미 만들어진 물비누, / 자체점도가 있고 거품, / 세정효과, 보습, 보존제포함</t>
-        </is>
-      </c>
-      <c r="F58" s="10" t="n"/>
+          <t>이미 만들어진 물비누 · 자체점도가 있고 거품 · 세정효과, 보습, 보존제포함</t>
+        </is>
+      </c>
+      <c r="F58" s="10" t="inlineStr"/>
     </row>
     <row r="59" ht="32" customHeight="1">
       <c r="A59" s="10" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E59" s="10" t="inlineStr">
         <is>
-          <t>어성초, 녹차, 자소엽추출물을 / 2:1:1비율로 섞은 원료</t>
+          <t>어성초, 녹차, 자소엽추출물을 · 2:1:1비율로 섞은 원료</t>
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t>녹차, / 어성초추출물</t>
+          <t>녹차 · 어성초추출물</t>
         </is>
       </c>
     </row>
@@ -7753,12 +7753,12 @@
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>모발 두피보습, 탄력 / 개인의 모발 및 두피상태에 따라 양을 조절해주세요.</t>
+          <t>모발 두피보습, 탄력 · 개인의 모발 및 두피상태에 따라 양을 조절해주세요.</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>다중)히아루론산, 에코보습제 / 글리세린 등</t>
+          <t>다중)히아루론산, 에코보습제 · 글리세린 등</t>
         </is>
       </c>
     </row>
@@ -7958,12 +7958,12 @@
       </c>
       <c r="E71" s="18" t="inlineStr">
         <is>
-          <t>어성초:녹차:자소엽=2:1:1 / 추출 후 저온 감압 농축, / 동결 건조 후 희석.</t>
+          <t>어성초:녹차:자소엽=2:1:1 · 추출 후 저온 감압 농축 · 동결 건조 후 희석.</t>
         </is>
       </c>
       <c r="F71" s="18" t="inlineStr">
         <is>
-          <t>녹차, / 어성초추출물</t>
+          <t>녹차 · 어성초추출물</t>
         </is>
       </c>
     </row>
@@ -7990,7 +7990,7 @@
       </c>
       <c r="E72" s="18" t="inlineStr">
         <is>
-          <t>로즈마리를 수증기 추출, / 로즈마리의 수용성 성분 다량.</t>
+          <t>로즈마리를 수증기 추출 · 로즈마리의 수용성 성분 다량.</t>
         </is>
       </c>
       <c r="F72" s="18" t="inlineStr">
@@ -8027,7 +8027,7 @@
       </c>
       <c r="F73" s="18" t="inlineStr">
         <is>
-          <t>1,2-헥산디올0.6g / (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
+          <t>1,2-헥산디올0.6g · (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -8196,10 +8196,10 @@
       </c>
       <c r="E82" s="10" t="inlineStr">
         <is>
-          <t>식물유래 98.24%함유, / 코코베타인, 애플계면활성제, / 라벤더워터, 판테놀 등 더 순한 샴푸베이스</t>
-        </is>
-      </c>
-      <c r="F82" s="10" t="n"/>
+          <t>식물유래 98.24%함유 · 코코베타인, 애플계면활성제 · 라벤더워터, 판테놀 등 더 순한 샴푸베이스</t>
+        </is>
+      </c>
+      <c r="F82" s="10" t="inlineStr"/>
     </row>
     <row r="83" ht="64" customHeight="1">
       <c r="A83" s="10" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="E83" s="10" t="inlineStr">
         <is>
-          <t>유기농 샐러리, 양배추, 현미 , 토마토추출물, / 순무, 당근, 브로컬리를 / 저온 추출 비타민 파괴를 최소화.</t>
+          <t>유기농 샐러리, 양배추, 현미 , 토마토추출물 · 순무, 당근, 브로컬리를 · 저온 추출 비타민 파괴를 최소화.</t>
         </is>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t>유기농 / 카밍 5솔루션</t>
+          <t>유기농 · 카밍 5솔루션</t>
         </is>
       </c>
     </row>
@@ -8256,12 +8256,12 @@
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>10g 중 네롤리에센셜오일, / 일랑일랑에센셜오일, 가용화제, 정제수, / 1,2 헥산디올, 카프릴릴글라이콜</t>
+          <t>10g 중 네롤리에센셜오일 · 일랑일랑에센셜오일, 가용화제, 정제수 · 1,2 헥산디올, 카프릴릴글라이콜</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>신생아일 / 경우 라벤더 / , 유기농 로먼 / 캐모마일에 / 센셜오일 1ml</t>
+          <t>신생아일 · 경우 라벤더 · 유기농 로먼 · 캐모마일에 · 센셜오일 1ml</t>
         </is>
       </c>
     </row>
@@ -8404,7 +8404,7 @@
           <t>애플계면활성제, 코코-베타인, 라벤더워터, 실크아미노산 등 더 순한 샴푸베이스.</t>
         </is>
       </c>
-      <c r="F93" s="18" t="n"/>
+      <c r="F93" s="18" t="inlineStr"/>
     </row>
     <row r="94" ht="32" customHeight="1">
       <c r="A94" s="18" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="F94" s="18" t="inlineStr">
         <is>
-          <t>원하는 / 추출물</t>
+          <t>원하는 · 추출물</t>
         </is>
       </c>
     </row>
@@ -8493,7 +8493,7 @@
       </c>
       <c r="E96" s="18" t="inlineStr">
         <is>
-          <t>보습,</t>
+          <t>보습</t>
         </is>
       </c>
       <c r="F96" s="18" t="inlineStr">
@@ -8701,10 +8701,10 @@
       </c>
       <c r="E107" s="10" t="inlineStr">
         <is>
-          <t>코코 베타인, 애플계면활성제, / 라벤더워터, 판테놀 등 / 더 순한 샴푸베이스</t>
-        </is>
-      </c>
-      <c r="F107" s="10" t="n"/>
+          <t>코코 베타인, 애플계면활성제 · 라벤더워터, 판테놀 등 · 더 순한 샴푸베이스</t>
+        </is>
+      </c>
+      <c r="F107" s="10" t="inlineStr"/>
     </row>
     <row r="108" ht="32" customHeight="1">
       <c r="A108" s="10" t="inlineStr">
@@ -8729,10 +8729,10 @@
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>두피 건강에 좋은 / 7가지 한방 약재 추출물</t>
-        </is>
-      </c>
-      <c r="F108" s="10" t="n"/>
+          <t>두피 건강에 좋은 · 7가지 한방 약재 추출물</t>
+        </is>
+      </c>
+      <c r="F108" s="10" t="inlineStr"/>
     </row>
     <row r="109" ht="16" customHeight="1">
       <c r="A109" s="10" t="inlineStr">
@@ -8760,7 +8760,7 @@
           <t>인삼 추출물</t>
         </is>
       </c>
-      <c r="F109" s="10" t="n"/>
+      <c r="F109" s="10" t="inlineStr"/>
     </row>
     <row r="110" ht="32" customHeight="1">
       <c r="A110" s="10" t="inlineStr">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="E110" s="10" t="inlineStr">
         <is>
-          <t>인삼 줄기세포 배양액, / 항산화</t>
+          <t>인삼 줄기세포 배양액 · 항산화</t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr">
@@ -8817,12 +8817,12 @@
       </c>
       <c r="E111" s="10" t="inlineStr">
         <is>
-          <t>시더우드, 라벤더, / 페퍼먼트, 레몬그라스EO를 / 블랜딩한 오일</t>
+          <t>시더우드, 라벤더 · 페퍼먼트, 레몬그라스EO를 · 블랜딩한 오일</t>
         </is>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t>시더우드EO, / 민트쿨 컴플렉스 / 블랜딩오일</t>
+          <t>시더우드EO · 민트쿨 컴플렉스 · 블랜딩오일</t>
         </is>
       </c>
     </row>
@@ -8959,10 +8959,10 @@
       </c>
       <c r="E120" s="18" t="inlineStr">
         <is>
-          <t>코코-베타인, 애플계면활성제, / 라벤더워터, 판테놀 등 / 민감성 두피, 베이비 전용 / 샴푸베이스</t>
-        </is>
-      </c>
-      <c r="F120" s="18" t="n"/>
+          <t>코코-베타인, 애플계면활성제 · 라벤더워터, 판테놀 등 · 민감성 두피, 베이비 전용 · 샴푸베이스</t>
+        </is>
+      </c>
+      <c r="F120" s="18" t="inlineStr"/>
     </row>
     <row r="121" ht="64" customHeight="1">
       <c r="A121" s="18" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="E121" s="18" t="inlineStr">
         <is>
-          <t>두피 건강에 좋은 / 진한 영양. / 8가지 국화산 처방 약재와 / 8가지 고산지대 허브. / 천연 식물의 복합 추출물</t>
+          <t>두피 건강에 좋은 · 진한 영양. · 8가지 국화산 처방 약재와 · 8가지 고산지대 허브. · 천연 식물의 복합 추출물</t>
         </is>
       </c>
       <c r="F121" s="18" t="inlineStr">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="E122" s="18" t="inlineStr">
         <is>
-          <t>모발 영양, 모발 탄력 / 실크 아미노산+마린 엘라스틴을 한번에</t>
+          <t>모발 영양, 모발 탄력 · 실크 아미노산+마린 엘라스틴을 한번에</t>
         </is>
       </c>
       <c r="F122" s="18" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="E123" s="18" t="inlineStr">
         <is>
-          <t>시더우드, 라벤더. / 페퍼민트, 레몬그라스EO를 / 복합 블랜딩한 오일</t>
+          <t>시더우드, 라벤더. · 페퍼민트, 레몬그라스EO를 · 복합 블랜딩한 오일</t>
         </is>
       </c>
       <c r="F123" s="18" t="inlineStr">
         <is>
-          <t>민트쿨 컴플렉스 / 블랜딩오일</t>
+          <t>민트쿨 컴플렉스 · 블랜딩오일</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
           <t>천연 점증제</t>
         </is>
       </c>
-      <c r="F132" s="10" t="n"/>
+      <c r="F132" s="10" t="inlineStr"/>
     </row>
     <row r="133" ht="48" customHeight="1">
       <c r="A133" s="10" t="inlineStr">
@@ -9265,12 +9265,12 @@
       </c>
       <c r="E134" s="10" t="inlineStr">
         <is>
-          <t>어성초, 자소엽, 녹차 추출물 / 항산화</t>
+          <t>어성초, 자소엽, 녹차 추출물 · 항산화</t>
         </is>
       </c>
       <c r="F134" s="10" t="inlineStr">
         <is>
-          <t>녹차, / 어성초추출물</t>
+          <t>녹차 · 어성초추출물</t>
         </is>
       </c>
     </row>
@@ -9297,7 +9297,7 @@
       </c>
       <c r="E135" s="10" t="inlineStr">
         <is>
-          <t>두피를 두껍게,</t>
+          <t>두피를 두껍게</t>
         </is>
       </c>
       <c r="F135" s="10" t="inlineStr">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="F136" s="10" t="inlineStr">
         <is>
-          <t>헥산디올2g / (추출물의양을 39g으로 줄여주세요.)</t>
+          <t>헥산디올2g · (추출물의양을 39g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -9366,7 +9366,7 @@
       </c>
       <c r="F137" s="10" t="inlineStr">
         <is>
-          <t>프리미엄 / 녹차워터</t>
+          <t>프리미엄 · 녹차워터</t>
         </is>
       </c>
     </row>
@@ -9525,12 +9525,12 @@
       </c>
       <c r="E147" s="18" t="inlineStr">
         <is>
-          <t>비건 인증, 순한 세정, / 두피 건강 덱스 판테놀</t>
+          <t>비건 인증, 순한 세정 · 두피 건강 덱스 판테놀</t>
         </is>
       </c>
       <c r="F147" s="18" t="inlineStr">
         <is>
-          <t>허브누리 / 순한 샴푸베이스</t>
+          <t>허브누리 · 순한 샴푸베이스</t>
         </is>
       </c>
     </row>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="E148" s="18" t="inlineStr">
         <is>
-          <t>병풀의 핵심 효능 성분,</t>
+          <t>병풀의 핵심 효능 성분</t>
         </is>
       </c>
       <c r="F148" s="18" t="inlineStr">
@@ -9594,7 +9594,7 @@
       </c>
       <c r="F149" s="18" t="inlineStr">
         <is>
-          <t>어성초 / , 카렌듈라추출물 등</t>
+          <t>어성초 · 카렌듈라추출물 등</t>
         </is>
       </c>
     </row>
@@ -9777,12 +9777,12 @@
       </c>
       <c r="E159" s="10" t="inlineStr">
         <is>
-          <t>슈퍼시카4, 덱스판테놀, / 실크아미노산, / 18가지 식물추출물 함유</t>
+          <t>슈퍼시카4, 덱스판테놀 · 실크아미노산 · 18가지 식물추출물 함유</t>
         </is>
       </c>
       <c r="F159" s="10" t="inlineStr">
         <is>
-          <t>허브누리 / 순한 샴푸베이스</t>
+          <t>허브누리 · 순한 샴푸베이스</t>
         </is>
       </c>
     </row>
@@ -9809,10 +9809,10 @@
       </c>
       <c r="E160" s="10" t="inlineStr">
         <is>
-          <t>아미노산 함유, / 모발두피를 건강하게</t>
-        </is>
-      </c>
-      <c r="F160" s="10" t="n"/>
+          <t>아미노산 함유 · 모발두피를 건강하게</t>
+        </is>
+      </c>
+      <c r="F160" s="10" t="inlineStr"/>
     </row>
     <row r="161" ht="32" customHeight="1">
       <c r="A161" s="10" t="inlineStr">
@@ -9837,7 +9837,7 @@
       </c>
       <c r="E161" s="10" t="inlineStr">
         <is>
-          <t>단백질 케어로 / 모발과 두피를 더 건강하게</t>
+          <t>단백질 케어로 · 모발과 두피를 더 건강하게</t>
         </is>
       </c>
       <c r="F161" s="10" t="inlineStr">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="E162" s="10" t="inlineStr">
         <is>
-          <t>레몬, 레몬그라스, / 로즈우드 / 에센셜오일 블렌딩</t>
+          <t>레몬, 레몬그라스 · 로즈우드 · 에센셜오일 블렌딩</t>
         </is>
       </c>
       <c r="F162" s="10" t="inlineStr">
         <is>
-          <t>민트쿨, 시더우드 / 블렌딩오일</t>
+          <t>민트쿨, 시더우드 · 블렌딩오일</t>
         </is>
       </c>
     </row>
@@ -10025,7 +10025,7 @@
       </c>
       <c r="E171" s="18" t="inlineStr">
         <is>
-          <t>짧은 구조로 빠른 흡수, / 가벼운 사용감, 촉촉함 오래</t>
+          <t>짧은 구조로 빠른 흡수 · 가벼운 사용감, 촉촉함 오래</t>
         </is>
       </c>
       <c r="F171" s="18" t="inlineStr">
@@ -10060,7 +10060,7 @@
           <t>유화 보조제</t>
         </is>
       </c>
-      <c r="F172" s="18" t="n"/>
+      <c r="F172" s="18" t="inlineStr"/>
     </row>
     <row r="173" ht="32" customHeight="1">
       <c r="A173" s="18" t="inlineStr">
@@ -10088,7 +10088,7 @@
           <t>유채유 유래 헤어제품 유화제, 정전기방지, 모발보습</t>
         </is>
       </c>
-      <c r="F173" s="18" t="n"/>
+      <c r="F173" s="18" t="inlineStr"/>
     </row>
     <row r="174" ht="64" customHeight="1">
       <c r="A174" s="18" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="E174" s="18" t="inlineStr">
         <is>
-          <t>보습, 피부타입에따라 줄이거나 늘려서 첨가 / ※3g이상 들어가면 스프레이보다는 펌핑용기에 담아사용하세요.</t>
+          <t>보습, 피부타입에따라 줄이거나 늘려서 첨가 · ※3g이상 들어가면 스프레이보다는 펌핑용기에 담아사용하세요.</t>
         </is>
       </c>
       <c r="F174" s="18" t="inlineStr">
@@ -10145,10 +10145,10 @@
       </c>
       <c r="E175" s="18" t="inlineStr">
         <is>
-          <t>양이온계면활성제, 정전기, / 모발을 부드럽게</t>
-        </is>
-      </c>
-      <c r="F175" s="18" t="n"/>
+          <t>양이온계면활성제, 정전기 · 모발을 부드럽게</t>
+        </is>
+      </c>
+      <c r="F175" s="18" t="inlineStr"/>
     </row>
     <row r="176" ht="64" customHeight="1">
       <c r="A176" s="18" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="F176" s="18" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -10210,7 +10210,7 @@
       </c>
       <c r="F177" s="18" t="inlineStr">
         <is>
-          <t>로즈마리, / 편백워터</t>
+          <t>로즈마리 · 편백워터</t>
         </is>
       </c>
     </row>
@@ -10237,7 +10237,7 @@
       </c>
       <c r="E178" s="18" t="inlineStr">
         <is>
-          <t>pH조절, / 구연산 1g + 정제수 9g</t>
+          <t>pH조절 · 구연산 1g + 정제수 9g</t>
         </is>
       </c>
       <c r="F178" s="18" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="E187" s="10" t="inlineStr">
         <is>
-          <t>슈퍼시카4, 덱스판테놀, / 실크아미노산, / 18가지 식물추출물 함유</t>
+          <t>슈퍼시카4, 덱스판테놀 · 실크아미노산 · 18가지 식물추출물 함유</t>
         </is>
       </c>
       <c r="F187" s="10" t="inlineStr">
         <is>
-          <t>허브누리 / 순한 샴푸베이스</t>
+          <t>허브누리 · 순한 샴푸베이스</t>
         </is>
       </c>
     </row>
@@ -10435,12 +10435,12 @@
       </c>
       <c r="E188" s="10" t="inlineStr">
         <is>
-          <t>호호바오일 리포좀, / 보습</t>
+          <t>호호바오일 리포좀 · 보습</t>
         </is>
       </c>
       <c r="F188" s="10" t="inlineStr">
         <is>
-          <t>슈퍼 곡물 / 단백질추출물</t>
+          <t>슈퍼 곡물 · 단백질추출물</t>
         </is>
       </c>
     </row>
@@ -10467,7 +10467,7 @@
       </c>
       <c r="E189" s="10" t="inlineStr">
         <is>
-          <t>단백질 케어로 / 모발과 두피를 더 건강하게</t>
+          <t>단백질 케어로 · 모발과 두피를 더 건강하게</t>
         </is>
       </c>
       <c r="F189" s="10" t="inlineStr">
@@ -10499,12 +10499,12 @@
       </c>
       <c r="E190" s="10" t="inlineStr">
         <is>
-          <t>레몬, 레몬그라스, / 로즈우드 / 에센셜오일 블렌딩</t>
+          <t>레몬, 레몬그라스 · 로즈우드 · 에센셜오일 블렌딩</t>
         </is>
       </c>
       <c r="F190" s="10" t="inlineStr">
         <is>
-          <t>라임캔디 / 블렌딩오일</t>
+          <t>라임캔디 · 블렌딩오일</t>
         </is>
       </c>
     </row>
@@ -10643,12 +10643,12 @@
       </c>
       <c r="E199" s="18" t="inlineStr">
         <is>
-          <t>슈퍼시카4, 덱스판테놀, / 실크아미노산, / 18가지 식물추출물 함유</t>
+          <t>슈퍼시카4, 덱스판테놀 · 실크아미노산 · 18가지 식물추출물 함유</t>
         </is>
       </c>
       <c r="F199" s="18" t="inlineStr">
         <is>
-          <t>허브누리 / 순한 샴푸베이스</t>
+          <t>허브누리 · 순한 샴푸베이스</t>
         </is>
       </c>
     </row>
@@ -10678,7 +10678,7 @@
           <t>비타민 풍부, 진정</t>
         </is>
       </c>
-      <c r="F200" s="18" t="n"/>
+      <c r="F200" s="18" t="inlineStr"/>
     </row>
     <row r="201" ht="32" customHeight="1">
       <c r="A201" s="18" t="inlineStr">
@@ -10703,12 +10703,12 @@
       </c>
       <c r="E201" s="18" t="inlineStr">
         <is>
-          <t>바다의 이슬이란 뜻에서 유래, / 혈액순환에 도움</t>
+          <t>바다의 이슬이란 뜻에서 유래 · 혈액순환에 도움</t>
         </is>
       </c>
       <c r="F201" s="18" t="inlineStr">
         <is>
-          <t>라벤더 / 에센셜오일</t>
+          <t>라벤더 · 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -10859,12 +10859,12 @@
       </c>
       <c r="E210" s="10" t="inlineStr">
         <is>
-          <t>슈퍼시카4, 덱스판테놀, / 실크아미노산, / 18가지 식물추출물 함유</t>
+          <t>슈퍼시카4, 덱스판테놀 · 실크아미노산 · 18가지 식물추출물 함유</t>
         </is>
       </c>
       <c r="F210" s="10" t="inlineStr">
         <is>
-          <t>허브누리 / 순한 샴푸베이스</t>
+          <t>허브누리 · 순한 샴푸베이스</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="E211" s="10" t="inlineStr">
         <is>
-          <t>약모밀, 빠른 진정효과, / 각종 트러블, 피부 개선에 사용</t>
+          <t>약모밀, 빠른 진정효과 · 각종 트러블, 피부 개선에 사용</t>
         </is>
       </c>
       <c r="F211" s="10" t="inlineStr">
@@ -10923,12 +10923,12 @@
       </c>
       <c r="E212" s="10" t="inlineStr">
         <is>
-          <t>티트리, 버가못FCF, 라벤더EO가 / 블렌딩된 오일</t>
+          <t>티트리, 버가못FCF, 라벤더EO가 · 블렌딩된 오일</t>
         </is>
       </c>
       <c r="F212" s="10" t="inlineStr">
         <is>
-          <t>라벤더, 티트리 / 에센셜오일</t>
+          <t>라벤더, 티트리 · 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -11071,12 +11071,12 @@
       </c>
       <c r="E221" s="18" t="inlineStr">
         <is>
-          <t>슈퍼시카4, 덱스판테놀, / 실크아미노산, / 18가지 식물추출물 함유</t>
+          <t>슈퍼시카4, 덱스판테놀 · 실크아미노산 · 18가지 식물추출물 함유</t>
         </is>
       </c>
       <c r="F221" s="18" t="inlineStr">
         <is>
-          <t>허브누리 / 순한 샴푸베이스</t>
+          <t>허브누리 · 순한 샴푸베이스</t>
         </is>
       </c>
     </row>
@@ -11103,16 +11103,16 @@
       </c>
       <c r="E222" s="18" t="inlineStr">
         <is>
-          <t>어성초, 녹차, 자소엽추출물을 / 2:1:1 비율로 섞은 원료</t>
+          <t>어성초, 녹차, 자소엽추출물을 · 2:1:1 비율로 섞은 원료</t>
         </is>
       </c>
       <c r="F222" s="18" t="inlineStr">
         <is>
-          <t>녹차, / 어성초추출물</t>
-        </is>
-      </c>
-    </row>
-    <row r="223" ht="64" customHeight="1">
+          <t>녹차 · 어성초추출물</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="48" customHeight="1">
       <c r="A223" s="18" t="inlineStr">
         <is>
           <t>프로바이오틱스 3</t>
@@ -11135,12 +11135,12 @@
       </c>
       <c r="E223" s="18" t="inlineStr">
         <is>
-          <t>락토바실러스 람노서스, 비피다발효용해물, / 락토코쿠스발효용해물 / 3가지 유산균 복합 성분</t>
+          <t>락토바실러스 람노서스, 비피다발효용해물 · 락토코쿠스발효용해물 · 3가지 유산균 복합 성분</t>
         </is>
       </c>
       <c r="F223" s="18" t="inlineStr">
         <is>
-          <t>비피다발효용해물, / 사카로미세스발효여과물</t>
+          <t>비피다발효용해물 · 사카로미세스발효여과물</t>
         </is>
       </c>
     </row>
@@ -11167,12 +11167,12 @@
       </c>
       <c r="E224" s="18" t="inlineStr">
         <is>
-          <t>허브의 여왕, / 진정, 재생, 항균</t>
+          <t>허브의 여왕 · 진정, 재생, 항균</t>
         </is>
       </c>
       <c r="F224" s="18" t="inlineStr">
         <is>
-          <t>로즈마리 / 에센셜오일</t>
+          <t>로즈마리 · 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -11321,7 +11321,7 @@
       </c>
       <c r="E233" s="10" t="inlineStr">
         <is>
-          <t>중쇄지방, 빠른 흡수, / 영양공급</t>
+          <t>중쇄지방, 빠른 흡수 · 영양공급</t>
         </is>
       </c>
       <c r="F233" s="10" t="inlineStr">
@@ -11353,10 +11353,10 @@
       </c>
       <c r="E234" s="10" t="inlineStr">
         <is>
-          <t>양이온유화제, 유연, / 정전기 방지, 모발,바디 사용</t>
-        </is>
-      </c>
-      <c r="F234" s="10" t="n"/>
+          <t>양이온유화제, 유연 · 정전기 방지, 모발,바디 사용</t>
+        </is>
+      </c>
+      <c r="F234" s="10" t="inlineStr"/>
     </row>
     <row r="235" ht="16" customHeight="1">
       <c r="A235" s="10" t="inlineStr">
@@ -11384,7 +11384,7 @@
           <t>유연,경화, 유화제</t>
         </is>
       </c>
-      <c r="F235" s="10" t="n"/>
+      <c r="F235" s="10" t="inlineStr"/>
     </row>
     <row r="236" ht="14" customHeight="1">
       <c r="A236" s="23" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="E244" s="18" t="inlineStr">
         <is>
-          <t>슈퍼시카4, 덱스판테놀, / 실크아미노산, / 18가지 식물추출물 함유</t>
+          <t>슈퍼시카4, 덱스판테놀 · 실크아미노산 · 18가지 식물추출물 함유</t>
         </is>
       </c>
       <c r="F244" s="18" t="inlineStr">
         <is>
-          <t>허브누리 / 순한 샴푸베이스</t>
+          <t>허브누리 · 순한 샴푸베이스</t>
         </is>
       </c>
     </row>
@@ -11565,10 +11565,10 @@
       </c>
       <c r="E245" s="18" t="inlineStr">
         <is>
-          <t>모발강화, / 비타민B7, 피부 진정</t>
-        </is>
-      </c>
-      <c r="F245" s="18" t="n"/>
+          <t>모발강화 · 비타민B7, 피부 진정</t>
+        </is>
+      </c>
+      <c r="F245" s="18" t="inlineStr"/>
     </row>
     <row r="246" ht="32" customHeight="1">
       <c r="A246" s="18" t="inlineStr">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="E246" s="18" t="inlineStr">
         <is>
-          <t>단백질 케어로 / 모발과 두피를 더 건강하게</t>
+          <t>단백질 케어로 · 모발과 두피를 더 건강하게</t>
         </is>
       </c>
       <c r="F246" s="18" t="inlineStr">
@@ -11625,12 +11625,12 @@
       </c>
       <c r="E247" s="18" t="inlineStr">
         <is>
-          <t>레몬, 레몬그라스, / 로즈우드 / 에센셜오일 블렌딩</t>
+          <t>레몬, 레몬그라스 · 로즈우드 · 에센셜오일 블렌딩</t>
         </is>
       </c>
       <c r="F247" s="18" t="inlineStr">
         <is>
-          <t>라임캔디 / 블렌딩오일</t>
+          <t>라임캔디 · 블렌딩오일</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="F256" s="10" t="inlineStr">
         <is>
-          <t>연핑크색 원하면 / 발효동백오일 84g, / 자초오일 6g 로 대체</t>
+          <t>연핑크색 원하면 · 발효동백오일 84g · 자초오일 6g 로 대체</t>
         </is>
       </c>
     </row>
@@ -11813,10 +11813,10 @@
       </c>
       <c r="E257" s="10" t="inlineStr">
         <is>
-          <t>유화제, 정전기 방지, / 물과 오일 섞임을 도와줌.</t>
-        </is>
-      </c>
-      <c r="F257" s="10" t="n"/>
+          <t>유화제, 정전기 방지 · 물과 오일 섞임을 도와줌.</t>
+        </is>
+      </c>
+      <c r="F257" s="10" t="inlineStr"/>
     </row>
     <row r="258" ht="16" customHeight="1">
       <c r="A258" s="10" t="inlineStr">
@@ -11844,7 +11844,7 @@
           <t>유화 보조, 단단함</t>
         </is>
       </c>
-      <c r="F258" s="10" t="n"/>
+      <c r="F258" s="10" t="inlineStr"/>
     </row>
     <row r="259" ht="32" customHeight="1">
       <c r="A259" s="10" t="inlineStr">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="E259" s="10" t="inlineStr">
         <is>
-          <t>장미 천연에센셜오일,</t>
+          <t>장미 천연에센셜오일</t>
         </is>
       </c>
       <c r="F259" s="10" t="inlineStr">
@@ -12021,12 +12021,12 @@
       </c>
       <c r="E268" s="18" t="inlineStr">
         <is>
-          <t>무향, / 병풀 핵심효능성분 4가지, 덱스 판테놀, / 순한 세정, 풍부한 거품 / ( / LES. 코코베타인, 라우릴글루코사이드,SCI) / , / 30여가지 허브성분, 저자극테스트완료</t>
+          <t>무향 · 병풀 핵심효능성분 4가지, 덱스 판테놀 · 순한 세정, 풍부한 거품 · ( · LES. 코코베타인, 라우릴글루코사이드,SCI) · 30여가지 허브성분, 저자극테스트완료</t>
         </is>
       </c>
       <c r="F268" s="18" t="inlineStr">
         <is>
-          <t>허브누리 / 순한 샴푸베이스</t>
+          <t>허브누리 · 순한 샴푸베이스</t>
         </is>
       </c>
     </row>
@@ -12053,10 +12053,10 @@
       </c>
       <c r="E269" s="18" t="inlineStr">
         <is>
-          <t>활력 카페인, 항산화 폴리페놀 풍부 / 고농축, 원두 우린 것을 동결건조, 물 없음</t>
-        </is>
-      </c>
-      <c r="F269" s="18" t="n"/>
+          <t>활력 카페인, 항산화 폴리페놀 풍부 · 고농축, 원두 우린 것을 동결건조, 물 없음</t>
+        </is>
+      </c>
+      <c r="F269" s="18" t="inlineStr"/>
     </row>
     <row r="270" ht="32" customHeight="1">
       <c r="A270" s="18" t="inlineStr">
@@ -12081,12 +12081,12 @@
       </c>
       <c r="E270" s="18" t="inlineStr">
         <is>
-          <t>허브의 고농축오일, / 시원, 커피와 시너지효과</t>
+          <t>허브의 고농축오일 · 시원, 커피와 시너지효과</t>
         </is>
       </c>
       <c r="F270" s="18" t="inlineStr">
         <is>
-          <t>로즈마리, / 라벤더에센셜오일 등</t>
+          <t>로즈마리 · 라벤더에센셜오일 등</t>
         </is>
       </c>
     </row>
@@ -12113,10 +12113,10 @@
       </c>
       <c r="E271" s="18" t="inlineStr">
         <is>
-          <t>어성초 함유, 스피아민트, 라벤더, / 로즈마리허브노일 함유 / 병풀 핵심효능성분 4가지, 덱스 판테놀, / 순한 세정, 풍부한 거품 / ( / LES. 코코베타인, 라우릴글루코사이드,SCI) / 15가지 유해성분 무첨가,</t>
-        </is>
-      </c>
-      <c r="F271" s="18" t="n"/>
+          <t>어성초 함유, 스피아민트, 라벤더 · 로즈마리허브노일 함유 · 병풀 핵심효능성분 4가지, 덱스 판테놀 · 순한 세정, 풍부한 거품 · ( · LES. 코코베타인, 라우릴글루코사이드,SCI) · 15가지 유해성분 무첨가</t>
+        </is>
+      </c>
+      <c r="F271" s="18" t="inlineStr"/>
     </row>
     <row r="272" ht="14" customHeight="1">
       <c r="A272" s="23" t="inlineStr">
@@ -12279,7 +12279,7 @@
           <t>약산성, 병풀추출물 함유</t>
         </is>
       </c>
-      <c r="F280" s="10" t="n"/>
+      <c r="F280" s="10" t="inlineStr"/>
     </row>
     <row r="281" ht="80" customHeight="1">
       <c r="A281" s="10" t="inlineStr">
@@ -12304,10 +12304,10 @@
       </c>
       <c r="E281" s="10" t="inlineStr">
         <is>
-          <t>2%, 박하 추출, 박하뇌, / 알코올, / 시원, 청량 / (양조절 가능, 1~5%) / 단, 많은 양 사용 시 / 따갑거나 화끈거림 등 피부 자극우려, / 테스트 후 적용</t>
-        </is>
-      </c>
-      <c r="F281" s="10" t="n"/>
+          <t>2%, 박하 추출, 박하뇌 · 알코올 · 시원, 청량 · (양조절 가능, 1~5%) · 단, 많은 양 사용 시 · 따갑거나 화끈거림 등 피부 자극우려 · 테스트 후 적용</t>
+        </is>
+      </c>
+      <c r="F281" s="10" t="inlineStr"/>
     </row>
     <row r="282" ht="16" customHeight="1">
       <c r="A282" s="10" t="inlineStr">
@@ -12335,7 +12335,7 @@
           <t>피부 트러블, 장벽튼튼, 매끈</t>
         </is>
       </c>
-      <c r="F282" s="10" t="n"/>
+      <c r="F282" s="10" t="inlineStr"/>
     </row>
     <row r="283" ht="48" customHeight="1">
       <c r="A283" s="10" t="inlineStr">
@@ -12365,7 +12365,7 @@
       </c>
       <c r="F283" s="10" t="inlineStr">
         <is>
-          <t>다중)히아루론산, 에코보습제 / 글리세린 등</t>
+          <t>다중)히아루론산, 에코보습제 · 글리세린 등</t>
         </is>
       </c>
     </row>
@@ -12545,10 +12545,10 @@
       </c>
       <c r="E293" s="18" t="inlineStr">
         <is>
-          <t>건강한 모발, 피부의 기준 약산성 / 병풀 함유, 비누베이스</t>
-        </is>
-      </c>
-      <c r="F293" s="18" t="n"/>
+          <t>건강한 모발, 피부의 기준 약산성 · 병풀 함유, 비누베이스</t>
+        </is>
+      </c>
+      <c r="F293" s="18" t="inlineStr"/>
     </row>
     <row r="294" ht="16" customHeight="1">
       <c r="A294" s="18" t="inlineStr">
@@ -12576,7 +12576,7 @@
           <t>로즈마리 잎 건조분말 1%</t>
         </is>
       </c>
-      <c r="F294" s="18" t="n"/>
+      <c r="F294" s="18" t="inlineStr"/>
     </row>
     <row r="295" ht="32" customHeight="1">
       <c r="A295" s="18" t="inlineStr">
@@ -12601,7 +12601,7 @@
       </c>
       <c r="E295" s="18" t="inlineStr">
         <is>
-          <t>로즈마리오일,</t>
+          <t>로즈마리오일</t>
         </is>
       </c>
       <c r="F295" s="18" t="inlineStr">
@@ -12633,7 +12633,7 @@
       </c>
       <c r="E296" s="18" t="inlineStr">
         <is>
-          <t>비타민B3, / 식약처 기능성 고시원료</t>
+          <t>비타민B3 · 식약처 기능성 고시원료</t>
         </is>
       </c>
       <c r="F296" s="18" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E297" s="18" t="inlineStr">
         <is>
-          <t>비타민B5, 모발보습, 두피건강 / 식약처 기능성 고시원료</t>
+          <t>비타민B5, 모발보습, 두피건강 · 식약처 기능성 고시원료</t>
         </is>
       </c>
       <c r="F297" s="18" t="inlineStr">
         <is>
-          <t>다중)히아루론산, 에코보습제 / 글리세린 등</t>
+          <t>다중)히아루론산, 에코보습제 · 글리세린 등</t>
         </is>
       </c>
     </row>
@@ -12697,10 +12697,10 @@
       </c>
       <c r="E298" s="18" t="inlineStr">
         <is>
-          <t>박하뇌, 청량감 / 식약처 기능성 고시원료</t>
-        </is>
-      </c>
-      <c r="F298" s="18" t="n"/>
+          <t>박하뇌, 청량감 · 식약처 기능성 고시원료</t>
+        </is>
+      </c>
+      <c r="F298" s="18" t="inlineStr"/>
     </row>
     <row r="299" ht="14" customHeight="1">
       <c r="A299" s="23" t="inlineStr">
@@ -12859,7 +12859,7 @@
       </c>
       <c r="F307" s="10" t="inlineStr">
         <is>
-          <t>허브누리 / 순한 샴푸베이스</t>
+          <t>허브누리 · 순한 샴푸베이스</t>
         </is>
       </c>
     </row>
@@ -12889,7 +12889,7 @@
           <t>모발강화, 탈모예방</t>
         </is>
       </c>
-      <c r="F308" s="10" t="n"/>
+      <c r="F308" s="10" t="inlineStr"/>
     </row>
     <row r="309" ht="32" customHeight="1">
       <c r="A309" s="10" t="inlineStr">
@@ -12919,7 +12919,7 @@
       </c>
       <c r="F309" s="10" t="inlineStr">
         <is>
-          <t>프리미엄 / 녹차워터</t>
+          <t>프리미엄 · 녹차워터</t>
         </is>
       </c>
     </row>
@@ -12983,7 +12983,7 @@
       </c>
       <c r="F311" s="10" t="inlineStr">
         <is>
-          <t>티트리(항균), / 스피아민트 등</t>
+          <t>티트리(항균) · 스피아민트 등</t>
         </is>
       </c>
     </row>
@@ -13131,7 +13131,7 @@
       </c>
       <c r="F320" s="18" t="inlineStr">
         <is>
-          <t>로즈마리, / 편백워터</t>
+          <t>로즈마리 · 편백워터</t>
         </is>
       </c>
     </row>
@@ -13161,7 +13161,7 @@
           <t>비듬, 가려움 완화 도움</t>
         </is>
       </c>
-      <c r="F321" s="18" t="n"/>
+      <c r="F321" s="18" t="inlineStr"/>
     </row>
     <row r="322" ht="32" customHeight="1">
       <c r="A322" s="18" t="inlineStr">
@@ -13191,7 +13191,7 @@
       </c>
       <c r="F322" s="18" t="inlineStr">
         <is>
-          <t>허브누리 / 순한 샴푸베이스</t>
+          <t>허브누리 · 순한 샴푸베이스</t>
         </is>
       </c>
     </row>
@@ -13255,7 +13255,7 @@
       </c>
       <c r="F324" s="18" t="inlineStr">
         <is>
-          <t>티트리(항균), / 스피아민트 등</t>
+          <t>티트리(항균) · 스피아민트 등</t>
         </is>
       </c>
     </row>
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E333" s="10" t="inlineStr">
         <is>
-          <t>약산성, 세정, / 자연유래 계면활성제</t>
+          <t>약산성, 세정 · 자연유래 계면활성제</t>
         </is>
       </c>
       <c r="F333" s="10" t="inlineStr">
         <is>
-          <t>허브누리 / 순한 샴푸베이스</t>
+          <t>허브누리 · 순한 샴푸베이스</t>
         </is>
       </c>
     </row>
@@ -13446,10 +13446,10 @@
       </c>
       <c r="E334" s="10" t="inlineStr">
         <is>
-          <t>스크럽, 노폐물, / 피지 삼투압으로 제거 도움</t>
-        </is>
-      </c>
-      <c r="F334" s="10" t="n"/>
+          <t>스크럽, 노폐물 · 피지 삼투압으로 제거 도움</t>
+        </is>
+      </c>
+      <c r="F334" s="10" t="inlineStr"/>
     </row>
     <row r="335" ht="32" customHeight="1">
       <c r="A335" s="10" t="inlineStr">
@@ -13511,7 +13511,7 @@
       </c>
       <c r="F336" s="10" t="inlineStr">
         <is>
-          <t>티트리(항균), / 스피아민트 등</t>
+          <t>티트리(항균) · 스피아민트 등</t>
         </is>
       </c>
     </row>
@@ -13651,12 +13651,12 @@
       </c>
       <c r="E345" s="18" t="inlineStr">
         <is>
-          <t>박하6(g), 감초4, 하수오6, 당귀2,약쑥6,삼백초4, 측백4g을 물500g을 넣고 2~3시간 담궈 놓는다. 약한 불에 반으로 줄 때까지 달인 후 / 체에 건더기를 걸러낸다. / 필요에 따라 물을 보충하면서 진하게 우려낸다.</t>
+          <t>박하6(g), 감초4, 하수오6, 당귀2,약쑥6,삼백초4, 측백4g을 물500g을 넣고 2~3시간 담궈 놓는다. 약한 불에 반으로 줄 때까지 달인 후 · 체에 건더기를 걸러낸다. · 필요에 따라 물을 보충하면서 진하게 우려낸다.</t>
         </is>
       </c>
       <c r="F345" s="18" t="inlineStr">
         <is>
-          <t>편백워터, / 라벤더워터 / 등..</t>
+          <t>편백워터 · 라벤더워터 · 등..</t>
         </is>
       </c>
     </row>
@@ -13683,10 +13683,10 @@
       </c>
       <c r="E346" s="18" t="inlineStr">
         <is>
-          <t>섬유질을 양이온화, 트리트먼트효과, / 많이 넣으면 잔존감, 두피가려음증 유발부작용</t>
-        </is>
-      </c>
-      <c r="F346" s="18" t="n"/>
+          <t>섬유질을 양이온화, 트리트먼트효과 · 많이 넣으면 잔존감, 두피가려음증 유발부작용</t>
+        </is>
+      </c>
+      <c r="F346" s="18" t="inlineStr"/>
     </row>
     <row r="347" ht="32" customHeight="1">
       <c r="A347" s="18" t="inlineStr">
@@ -13711,10 +13711,10 @@
       </c>
       <c r="E347" s="18" t="inlineStr">
         <is>
-          <t>옥수수전분으로 만든 점증제, 젤화,자체보습 / Non GMO</t>
-        </is>
-      </c>
-      <c r="F347" s="18" t="n"/>
+          <t>옥수수전분으로 만든 점증제, 젤화,자체보습 · Non GMO</t>
+        </is>
+      </c>
+      <c r="F347" s="18" t="inlineStr"/>
     </row>
     <row r="348" ht="48" customHeight="1">
       <c r="A348" s="18" t="inlineStr">
@@ -13739,7 +13739,7 @@
       </c>
       <c r="E348" s="18" t="inlineStr">
         <is>
-          <t>음이온 계면활성제, 거품, 세정력,</t>
+          <t>음이온 계면활성제, 거품, 세정력</t>
         </is>
       </c>
       <c r="F348" s="18" t="inlineStr">
@@ -13748,7 +13748,7 @@
         </is>
       </c>
     </row>
-    <row r="349" ht="48" customHeight="1">
+    <row r="349" ht="32" customHeight="1">
       <c r="A349" s="18" t="inlineStr">
         <is>
           <t>코코 -베타인</t>
@@ -13771,12 +13771,12 @@
       </c>
       <c r="E349" s="18" t="inlineStr">
         <is>
-          <t>양쪽성 계면활성제, 자극이 적고 살균효과, / 모발 정전기 방지</t>
+          <t>양쪽성 계면활성제, 자극이 적고 살균효과 · 모발 정전기 방지</t>
         </is>
       </c>
       <c r="F349" s="18" t="inlineStr">
         <is>
-          <t>애플 / 계면활성제</t>
+          <t>애플 · 계면활성제</t>
         </is>
       </c>
     </row>
@@ -13806,7 +13806,7 @@
           <t>누에추출 실크 가수분해, 모발과 피부친화, 유연</t>
         </is>
       </c>
-      <c r="F350" s="18" t="n"/>
+      <c r="F350" s="18" t="inlineStr"/>
     </row>
     <row r="351" ht="16" customHeight="1">
       <c r="A351" s="18" t="inlineStr">
@@ -13834,7 +13834,7 @@
           <t>모발, 두피 탄력</t>
         </is>
       </c>
-      <c r="F351" s="18" t="n"/>
+      <c r="F351" s="18" t="inlineStr"/>
     </row>
     <row r="352" ht="32" customHeight="1">
       <c r="A352" s="18" t="inlineStr">
@@ -13896,7 +13896,7 @@
       </c>
       <c r="F353" s="18" t="inlineStr">
         <is>
-          <t>1,2-헥산디올10g / (7가지한방약재 달인물의 양을 245g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올10g · (7가지한방약재 달인물의 양을 245g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -13923,7 +13923,7 @@
       </c>
       <c r="E354" s="18" t="inlineStr">
         <is>
-          <t>시더우드 잎을 수증기 추출법으로 추출, / 지루성 두피관리, / 항균, 비듬균 강력한 효과 / (허브누리 실험보고서 참고)</t>
+          <t>시더우드 잎을 수증기 추출법으로 추출 · 지루성 두피관리 · 항균, 비듬균 강력한 효과 · (허브누리 실험보고서 참고)</t>
         </is>
       </c>
       <c r="F354" s="18" t="inlineStr">
@@ -14125,7 +14125,7 @@
           <t>약산성 비누베이스</t>
         </is>
       </c>
-      <c r="F364" s="10" t="n"/>
+      <c r="F364" s="10" t="inlineStr"/>
     </row>
     <row r="365" ht="32" customHeight="1">
       <c r="A365" s="10" t="inlineStr">
@@ -14153,7 +14153,7 @@
           <t>식물유래 유황, 피부를 매끄럽게</t>
         </is>
       </c>
-      <c r="F365" s="10" t="n"/>
+      <c r="F365" s="10" t="inlineStr"/>
     </row>
     <row r="366" ht="48" customHeight="1">
       <c r="A366" s="10" t="inlineStr">
@@ -14178,10 +14178,10 @@
       </c>
       <c r="E366" s="10" t="inlineStr">
         <is>
-          <t>풍부한 비타민C, 색 빠짐 방지 / 모발 강화 및 윤기, 두피 건강</t>
-        </is>
-      </c>
-      <c r="F366" s="10" t="n"/>
+          <t>풍부한 비타민C, 색 빠짐 방지 · 모발 강화 및 윤기, 두피 건강</t>
+        </is>
+      </c>
+      <c r="F366" s="10" t="inlineStr"/>
     </row>
     <row r="367" ht="16" customHeight="1">
       <c r="A367" s="10" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="E377" s="18" t="inlineStr">
         <is>
-          <t>사탕무우 얻어 지는 다당류의 천연성분. 눈이나 피부에 자극이 없는 비이온계, / 베이비샴푸나 식물성 샴푸의 세정력을 높여주는 역할을 하는 천연계면활성제</t>
+          <t>사탕무우 얻어 지는 다당류의 천연성분. 눈이나 피부에 자극이 없는 비이온계 · 베이비샴푸나 식물성 샴푸의 세정력을 높여주는 역할을 하는 천연계면활성제</t>
         </is>
       </c>
       <c r="F377" s="18" t="inlineStr">
@@ -14486,7 +14486,7 @@
       </c>
       <c r="F380" s="18" t="inlineStr">
         <is>
-          <t>알란토인, / 감초추출물</t>
+          <t>알란토인 · 감초추출물</t>
         </is>
       </c>
     </row>
@@ -14513,12 +14513,12 @@
       </c>
       <c r="E381" s="18" t="inlineStr">
         <is>
-          <t>보습, 촉촉함이 오래유지, / 피부보호막</t>
+          <t>보습, 촉촉함이 오래유지 · 피부보호막</t>
         </is>
       </c>
       <c r="F381" s="18" t="inlineStr">
         <is>
-          <t>스쿠알란, / 보르피린</t>
+          <t>스쿠알란 · 보르피린</t>
         </is>
       </c>
     </row>
@@ -14577,12 +14577,12 @@
       </c>
       <c r="E383" s="18" t="inlineStr">
         <is>
-          <t>귤껍질오일, / 임신기간 영아에게 안전하게 사용, / 모든 피부사용</t>
+          <t>귤껍질오일 · 임신기간 영아에게 안전하게 사용 · 모든 피부사용</t>
         </is>
       </c>
       <c r="F383" s="18" t="inlineStr">
         <is>
-          <t>라벤더, / 로먼캐모마일 / 에센셜오일</t>
+          <t>라벤더 · 로먼캐모마일 · 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -14735,7 +14735,7 @@
           <t>박하, 감초, 하수오, 당귀, 약쑥, 삼백초, 측백</t>
         </is>
       </c>
-      <c r="F392" s="10" t="n"/>
+      <c r="F392" s="10" t="inlineStr"/>
     </row>
     <row r="393" ht="16" customHeight="1">
       <c r="A393" s="10" t="inlineStr">
@@ -14936,7 +14936,7 @@
       </c>
       <c r="E403" s="18" t="inlineStr">
         <is>
-          <t>캐모마일 꽃을 수증기증류해 얻음. / 민감한 두피진정 / [주의] 캐모마일을 우린 물이나 한방약재를 우린 물을 넣을 경우 거품용기가 막히는 경우가 자주있습니다.</t>
+          <t>캐모마일 꽃을 수증기증류해 얻음. · 민감한 두피진정 · [주의] 캐모마일을 우린 물이나 한방약재를 우린 물을 넣을 경우 거품용기가 막히는 경우가 자주있습니다.</t>
         </is>
       </c>
       <c r="F403" s="18" t="inlineStr">
@@ -15000,7 +15000,7 @@
       </c>
       <c r="E405" s="18" t="inlineStr">
         <is>
-          <t>한방 추출물 국화산(감국, 만형자, 측백엽, 천궁, 백지, 세신, 상백피, 한련초) + / Mexico 고산지대 천연 식물추출물(호호바, 에스피노질리아, 호두, 아보카도, 알로에, 카모마일, 네틀, 엘더베리)의 혼합추출물이다. / 모근, 모발에 영양공급, 백모,탈모, 육모 등을 관리할 수 있도록 개발된 원료</t>
+          <t>한방 추출물 국화산(감국, 만형자, 측백엽, 천궁, 백지, 세신, 상백피, 한련초) + · Mexico 고산지대 천연 식물추출물(호호바, 에스피노질리아, 호두, 아보카도, 알로에, 카모마일, 네틀, 엘더베리)의 혼합추출물이다. · 모근, 모발에 영양공급, 백모,탈모, 육모 등을 관리할 수 있도록 개발된 원료</t>
         </is>
       </c>
       <c r="F405" s="18" t="inlineStr">
@@ -15032,7 +15032,7 @@
       </c>
       <c r="E406" s="18" t="inlineStr">
         <is>
-          <t>쿠퍼펩타이드는 사람의 혈액, 침 등에서 발견되는 인체 유래의 천연펩타이드입니다. / 노화가 진행됨에 따라 감소 현상을 보이게 됩니다. 쿠퍼펩타이드는 손상된 콜라겐이나 엘 라스틴을 제거하고, 줄기세포(stem cell)를 생성을 돕습니다. 또한 두피를 두껍게 만들어 모근을 건강하게 만들어줍니다.</t>
+          <t>쿠퍼펩타이드는 사람의 혈액, 침 등에서 발견되는 인체 유래의 천연펩타이드입니다. · 노화가 진행됨에 따라 감소 현상을 보이게 됩니다. 쿠퍼펩타이드는 손상된 콜라겐이나 엘 라스틴을 제거하고, 줄기세포(stem cell)를 생성을 돕습니다. 또한 두피를 두껍게 만들어 모근을 건강하게 만들어줍니다.</t>
         </is>
       </c>
       <c r="F406" s="18" t="inlineStr">
@@ -15069,7 +15069,7 @@
       </c>
       <c r="F407" s="18" t="inlineStr">
         <is>
-          <t>1,2-헥산디올5g / (네롤리워터의 양을 93g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올5g · (네롤리워터의 양을 93g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -15096,7 +15096,7 @@
       </c>
       <c r="E408" s="18" t="inlineStr">
         <is>
-          <t>1%, 지루성두피, / 허브누리 실험실 참고.</t>
+          <t>1%, 지루성두피 · 허브누리 실험실 참고.</t>
         </is>
       </c>
       <c r="F408" s="18" t="inlineStr">
@@ -15289,12 +15289,12 @@
       </c>
       <c r="E418" s="10" t="inlineStr">
         <is>
-          <t>에코인증 올리브오일유래. / 물과 오일 분리저지, 보습</t>
+          <t>에코인증 올리브오일유래. · 물과 오일 분리저지, 보습</t>
         </is>
       </c>
       <c r="F418" s="10" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -15324,7 +15324,7 @@
           <t>점증제, 유화보조제, 보습</t>
         </is>
       </c>
-      <c r="F419" s="10" t="n"/>
+      <c r="F419" s="10" t="inlineStr"/>
     </row>
     <row r="420" ht="16" customHeight="1">
       <c r="A420" s="10" t="inlineStr">
@@ -15381,10 +15381,10 @@
       </c>
       <c r="E421" s="10" t="inlineStr">
         <is>
-          <t>엘라스틴은 무정형 형태의 단백질로 피부의 탱탱함을 유지하는 역할 , 심해어류에서 분리정제한 엘라스틴 / 단백질</t>
-        </is>
-      </c>
-      <c r="F421" s="10" t="n"/>
+          <t>엘라스틴은 무정형 형태의 단백질로 피부의 탱탱함을 유지하는 역할 , 심해어류에서 분리정제한 엘라스틴 · 단백질</t>
+        </is>
+      </c>
+      <c r="F421" s="10" t="inlineStr"/>
     </row>
     <row r="422" ht="112" customHeight="1">
       <c r="A422" s="10" t="inlineStr">
@@ -15409,10 +15409,10 @@
       </c>
       <c r="E422" s="10" t="inlineStr">
         <is>
-          <t>인간의 피부나 모발을 구성하는 아미노산 조성비 와 유사하는 것으로부터 , 피부나 모발에 높은 친화성을 가지고 있습니다. / 실크 파우더는 누에에서는 나오는 실크를 가수 분해하여 고분자로 만든 것입니다.</t>
-        </is>
-      </c>
-      <c r="F422" s="10" t="n"/>
+          <t>인간의 피부나 모발을 구성하는 아미노산 조성비 와 유사하는 것으로부터 , 피부나 모발에 높은 친화성을 가지고 있습니다. · 실크 파우더는 누에에서는 나오는 실크를 가수 분해하여 고분자로 만든 것입니다.</t>
+        </is>
+      </c>
+      <c r="F422" s="10" t="inlineStr"/>
     </row>
     <row r="423" ht="16" customHeight="1">
       <c r="A423" s="10" t="inlineStr">
@@ -15706,7 +15706,7 @@
           <t>에스피노질리아 허브 추출, 두피·모발 강화</t>
         </is>
       </c>
-      <c r="F436" s="18" t="n"/>
+      <c r="F436" s="18" t="inlineStr"/>
     </row>
     <row r="437" ht="16" customHeight="1">
       <c r="A437" s="18" t="inlineStr">
@@ -15730,7 +15730,7 @@
           <t>쐐기풀 추출, 두피·피지 조절</t>
         </is>
       </c>
-      <c r="F437" s="18" t="n"/>
+      <c r="F437" s="18" t="inlineStr"/>
     </row>
     <row r="438" ht="48" customHeight="1">
       <c r="A438" s="18" t="inlineStr">
@@ -15779,12 +15779,12 @@
       </c>
       <c r="E439" s="18" t="inlineStr">
         <is>
-          <t>샴푸베이스에 이미 있지만 추가 보습을 원하면 모발 보습제로 넣어주세요. / 모발, 두피 보습제, / 좀더 모발을 부드럽게, 많은 양을 넣을 경우 점도가 묽어짐.</t>
+          <t>샴푸베이스에 이미 있지만 추가 보습을 원하면 모발 보습제로 넣어주세요. · 모발, 두피 보습제 · 좀더 모발을 부드럽게, 많은 양을 넣을 경우 점도가 묽어짐.</t>
         </is>
       </c>
       <c r="F439" s="18" t="inlineStr">
         <is>
-          <t>다중)히아루론산, 에코보습제 / 글리세린 등</t>
+          <t>다중)히아루론산, 에코보습제 · 글리세린 등</t>
         </is>
       </c>
     </row>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="F440" s="18" t="inlineStr">
         <is>
-          <t>네롤리,카모마일저먼 / (:일때 양을줄임-2방울), / 로먼카모마일 등</t>
+          <t>네롤리,카모마일저먼 · (:일때 양을줄임-2방울) · 로먼카모마일 등</t>
         </is>
       </c>
     </row>
@@ -15835,7 +15835,7 @@
       </c>
       <c r="E441" s="18" t="inlineStr">
         <is>
-          <t>바다의 이슬이란 뜻에서 유래, / 혈액순환에 도움</t>
+          <t>바다의 이슬이란 뜻에서 유래 · 혈액순환에 도움</t>
         </is>
       </c>
       <c r="F441" s="18" t="inlineStr">
@@ -15866,7 +15866,7 @@
           <t>레몬글라스 잎을 비벼보면 레몬향이 남, 공기정화 , 벌레퇴치</t>
         </is>
       </c>
-      <c r="F442" s="18" t="n"/>
+      <c r="F442" s="18" t="inlineStr"/>
     </row>
     <row r="443" ht="14" customHeight="1">
       <c r="A443" s="15" t="inlineStr">
@@ -15962,10 +15962,10 @@
       </c>
       <c r="E448" s="10" t="inlineStr">
         <is>
-          <t>이미 만들어진 물비누, / 자체점도가 있고 거품, / 세정효과, 보습, 보존제포함</t>
-        </is>
-      </c>
-      <c r="F448" s="10" t="n"/>
+          <t>이미 만들어진 물비누 · 자체점도가 있고 거품 · 세정효과, 보습, 보존제포함</t>
+        </is>
+      </c>
+      <c r="F448" s="10" t="inlineStr"/>
     </row>
     <row r="449" ht="48" customHeight="1">
       <c r="A449" s="10" t="inlineStr">
@@ -16022,10 +16022,10 @@
       </c>
       <c r="E450" s="10" t="inlineStr">
         <is>
-          <t>예로부터 두피탈모관련 / 한약재로 사용</t>
-        </is>
-      </c>
-      <c r="F450" s="10" t="n"/>
+          <t>예로부터 두피탈모관련 · 한약재로 사용</t>
+        </is>
+      </c>
+      <c r="F450" s="10" t="inlineStr"/>
     </row>
     <row r="451" ht="96" customHeight="1">
       <c r="A451" s="10" t="inlineStr">
@@ -16050,12 +16050,12 @@
       </c>
       <c r="E451" s="10" t="inlineStr">
         <is>
-          <t>샴푸베이스에 이미 있지만 추가 보습을 원하면 모발 보습제로 넣어주세요. / 모발, 두피 보습제, / 좀더 모발을 부드럽게, 많은 양을 넣을 경우 점도가 묽어짐.</t>
+          <t>샴푸베이스에 이미 있지만 추가 보습을 원하면 모발 보습제로 넣어주세요. · 모발, 두피 보습제 · 좀더 모발을 부드럽게, 많은 양을 넣을 경우 점도가 묽어짐.</t>
         </is>
       </c>
       <c r="F451" s="10" t="inlineStr">
         <is>
-          <t>다중)히아루론산, 에코보습제 / 글리세린 등</t>
+          <t>다중)히아루론산, 에코보습제 · 글리세린 등</t>
         </is>
       </c>
     </row>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="E452" s="10" t="inlineStr">
         <is>
-          <t>페퍼민트 EO, 로즈마리 EO, / 라벤더 EO 복합 블랜딩한 오일 / [주의 : 임신기간 중이거나 고혈압이 있는 분들은 다른 아로마오일을 / 사용할 것 ]</t>
+          <t>페퍼민트 EO, 로즈마리 EO · 라벤더 EO 복합 블랜딩한 오일 · [주의 : 임신기간 중이거나 고혈압이 있는 분들은 다른 아로마오일을 · 사용할 것 ]</t>
         </is>
       </c>
       <c r="F452" s="10" t="inlineStr">
@@ -16248,7 +16248,7 @@
       </c>
       <c r="E462" s="18" t="inlineStr">
         <is>
-          <t>롤볼 기준 높이 5.5cm까지 골든 호호바오일을 넣어주시면 8.6g(=10ml) / 골든 호호바오일,사람피지성분과 비슷, 끈적임없이 흡수, 액상왁스, 비타민E함유.</t>
+          <t>롤볼 기준 높이 5.5cm까지 골든 호호바오일을 넣어주시면 8.6g(=10ml) · 골든 호호바오일,사람피지성분과 비슷, 끈적임없이 흡수, 액상왁스, 비타민E함유.</t>
         </is>
       </c>
       <c r="F462" s="18" t="inlineStr">
@@ -16276,7 +16276,7 @@
       </c>
       <c r="E463" s="18" t="inlineStr">
         <is>
-          <t>올레인산 다량함유, 피부장벽강화, 항산화효과 베이비, / 민감 성피부</t>
+          <t>올레인산 다량함유, 피부장벽강화, 항산화효과 베이비 · 민감 성피부</t>
         </is>
       </c>
       <c r="F463" s="18" t="inlineStr">
@@ -16309,7 +16309,7 @@
       </c>
       <c r="F464" s="18" t="inlineStr">
         <is>
-          <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
+          <t>카렌듈라,달맞이오일 · 보리지오일,동백오일 · 호호바오일 등</t>
         </is>
       </c>
     </row>
@@ -16332,7 +16332,7 @@
       </c>
       <c r="E465" s="18" t="inlineStr">
         <is>
-          <t>바다의 이슬이란 뜻에서 유래, / 혈액순환에 도움</t>
+          <t>바다의 이슬이란 뜻에서 유래 · 혈액순환에 도움</t>
         </is>
       </c>
       <c r="F465" s="18" t="inlineStr">
@@ -16494,7 +16494,7 @@
       </c>
       <c r="F474" s="10" t="inlineStr">
         <is>
-          <t>프리미엄 / 녹차워터</t>
+          <t>프리미엄 · 녹차워터</t>
         </is>
       </c>
     </row>
@@ -16517,7 +16517,7 @@
       </c>
       <c r="E475" s="10" t="inlineStr">
         <is>
-          <t>구연산: 정제수=1:9 pH 조절 / (주방세제는 pH 10~6 가능)</t>
+          <t>구연산: 정제수=1:9 pH 조절 · (주방세제는 pH 10~6 가능)</t>
         </is>
       </c>
       <c r="F475" s="10" t="inlineStr">
@@ -16545,7 +16545,7 @@
       </c>
       <c r="E476" s="10" t="inlineStr">
         <is>
-          <t>보습, 피부타입에따라 줄이거나 늘려서 첨가 / ※3g이상 들어가면 스프레이보다는 펌핑용기에 담아사용하세요.</t>
+          <t>보습, 피부타입에따라 줄이거나 늘려서 첨가 · ※3g이상 들어가면 스프레이보다는 펌핑용기에 담아사용하세요.</t>
         </is>
       </c>
       <c r="F476" s="10" t="inlineStr">
@@ -16661,7 +16661,7 @@
       </c>
       <c r="E484" s="18" t="inlineStr">
         <is>
-          <t>올레인산 다량함유, 피부장벽강화, 항산화효과 베이비, / 민감 성피부</t>
+          <t>올레인산 다량함유, 피부장벽강화, 항산화효과 베이비 · 민감 성피부</t>
         </is>
       </c>
       <c r="F484" s="18" t="inlineStr">
@@ -16689,7 +16689,7 @@
       </c>
       <c r="E485" s="18" t="inlineStr">
         <is>
-          <t>롤볼 기준 높이 5.5cm까지 골든 호호바오일을 넣어주시면 8.6g(=10ml) / 골든 호호바오일,사람피지성분과 비슷, 끈적임없이 흡수, 액상왁스, 비타민E함유.</t>
+          <t>롤볼 기준 높이 5.5cm까지 골든 호호바오일을 넣어주시면 8.6g(=10ml) · 골든 호호바오일,사람피지성분과 비슷, 끈적임없이 흡수, 액상왁스, 비타민E함유.</t>
         </is>
       </c>
       <c r="F485" s="18" t="inlineStr">
@@ -16722,7 +16722,7 @@
       </c>
       <c r="F486" s="18" t="inlineStr">
         <is>
-          <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
+          <t>카렌듈라,달맞이오일 · 보리지오일,동백오일 · 호호바오일 등</t>
         </is>
       </c>
     </row>
@@ -16750,7 +16750,7 @@
       </c>
       <c r="F487" s="18" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -16806,7 +16806,7 @@
       </c>
       <c r="F489" s="18" t="inlineStr">
         <is>
-          <t>프리미엄 / 녹차워터</t>
+          <t>프리미엄 · 녹차워터</t>
         </is>
       </c>
     </row>
@@ -16829,12 +16829,12 @@
       </c>
       <c r="E490" s="18" t="inlineStr">
         <is>
-          <t>샴푸베이스에 이미 있지만 추가 보습을 원하면 모발 보습제로 넣어주세요. / 모발, 두피 보습제, / 좀더 모발을 부드럽게, 많은 양을 넣을 경우 점도가 묽어짐.</t>
+          <t>샴푸베이스에 이미 있지만 추가 보습을 원하면 모발 보습제로 넣어주세요. · 모발, 두피 보습제 · 좀더 모발을 부드럽게, 많은 양을 넣을 경우 점도가 묽어짐.</t>
         </is>
       </c>
       <c r="F490" s="18" t="inlineStr">
         <is>
-          <t>다중)히아루론산, 에코보습제 / 글리세린 등</t>
+          <t>다중)히아루론산, 에코보습제 · 글리세린 등</t>
         </is>
       </c>
     </row>
@@ -16857,10 +16857,10 @@
       </c>
       <c r="E491" s="18" t="inlineStr">
         <is>
-          <t>엘라스틴은 무정형 형태의 단백질로 피부의 탱탱함을 유지하는 역할 , 심해어류에서 분리정제한 엘라스틴 / 단백질</t>
-        </is>
-      </c>
-      <c r="F491" s="18" t="n"/>
+          <t>엘라스틴은 무정형 형태의 단백질로 피부의 탱탱함을 유지하는 역할 , 심해어류에서 분리정제한 엘라스틴 · 단백질</t>
+        </is>
+      </c>
+      <c r="F491" s="18" t="inlineStr"/>
     </row>
     <row r="492" ht="112" customHeight="1">
       <c r="A492" s="18" t="inlineStr">
@@ -16881,10 +16881,10 @@
       </c>
       <c r="E492" s="18" t="inlineStr">
         <is>
-          <t>인간의 피부나 모발을 구성하는 아미노산 조성비 와 유사하는 것으로부터 , 피부나 모발에 높은 친화성을 가지고 있습니다. / 실크 파우더는 누에에서는 나오는 실크를 가수 분해하여 고분자로 만든 것입니다.</t>
-        </is>
-      </c>
-      <c r="F492" s="18" t="n"/>
+          <t>인간의 피부나 모발을 구성하는 아미노산 조성비 와 유사하는 것으로부터 , 피부나 모발에 높은 친화성을 가지고 있습니다. · 실크 파우더는 누에에서는 나오는 실크를 가수 분해하여 고분자로 만든 것입니다.</t>
+        </is>
+      </c>
+      <c r="F492" s="18" t="inlineStr"/>
     </row>
     <row r="493" ht="48" customHeight="1">
       <c r="A493" s="18" t="inlineStr">
@@ -16905,12 +16905,12 @@
       </c>
       <c r="E493" s="18" t="inlineStr">
         <is>
-          <t>사탕무(보습)에서 추출한 당+코코넛오일 로 / 만든 양쪽성 계면활성제</t>
+          <t>사탕무(보습)에서 추출한 당+코코넛오일 로 · 만든 양쪽성 계면활성제</t>
         </is>
       </c>
       <c r="F493" s="18" t="inlineStr">
         <is>
-          <t>애플 / 계면활성제</t>
+          <t>애플 · 계면활성제</t>
         </is>
       </c>
     </row>
@@ -16961,12 +16961,12 @@
       </c>
       <c r="E495" s="18" t="inlineStr">
         <is>
-          <t>허브의 고농축오일, / 시원, 커피와 시너지효과</t>
+          <t>허브의 고농축오일 · 시원, 커피와 시너지효과</t>
         </is>
       </c>
       <c r="F495" s="18" t="inlineStr">
         <is>
-          <t>티트리(항균), / 스피아민트 등</t>
+          <t>티트리(항균) · 스피아민트 등</t>
         </is>
       </c>
     </row>
